--- a/rtss-pre1917/src/main/resources/excel-templates/composite-taxon-1881-1914.xlsx
+++ b/rtss-pre1917/src/main/resources/excel-templates/composite-taxon-1881-1914.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\excel-templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B268E7-8BF6-4048-BA8D-5F70FB185BCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D415170-33DB-4BCF-B5F3-63E19DB95152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" xr2:uid="{BB18BFB1-C03A-41FE-BE1A-93D139757D6D}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{BB18BFB1-C03A-41FE-BE1A-93D139757D6D}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
   <si>
     <t>XXX</t>
   </si>
@@ -109,6 +109,15 @@
   </si>
   <si>
     <t>%учёта</t>
+  </si>
+  <si>
+    <t>эмигр</t>
+  </si>
+  <si>
+    <t>иммигр</t>
+  </si>
+  <si>
+    <t>внутр. мигр</t>
   </si>
 </sst>
 </file>
@@ -198,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -228,11 +237,12 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -339,7 +349,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>data!$I$4</c:f>
+              <c:f>data!$M$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -488,7 +498,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>data!$I$5:$I$39</c:f>
+              <c:f>data!$M$5:$M$39</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="35"/>
@@ -609,7 +619,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>data!$J$4</c:f>
+              <c:f>data!$N$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -758,7 +768,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>data!$J$5:$J$39</c:f>
+              <c:f>data!$N$5:$N$39</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="35"/>
@@ -879,7 +889,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>data!$K$4</c:f>
+              <c:f>data!$O$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1028,7 +1038,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>data!$K$5:$K$39</c:f>
+              <c:f>data!$O$5:$O$39</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="35"/>
@@ -3035,16 +3045,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>284797</xdr:rowOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>10477</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>619125</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3071,16 +3081,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>952</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>170497</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>810577</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>20002</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>617220</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>628650</xdr:colOff>
+      <xdr:row>144</xdr:row>
+      <xdr:rowOff>150495</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3425,34 +3435,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12B321D7-C433-4B50-AA6E-BF1C75F28F7F}">
-  <dimension ref="A1:L42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S42"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" customWidth="1"/>
-    <col min="5" max="5" width="15.5703125" customWidth="1"/>
-    <col min="6" max="7" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.85546875" customWidth="1"/>
+    <col min="1" max="1" width="11.26171875" customWidth="1"/>
+    <col min="2" max="2" width="14.578125" customWidth="1"/>
+    <col min="3" max="3" width="16.26171875" customWidth="1"/>
+    <col min="4" max="4" width="11.62890625" customWidth="1"/>
+    <col min="5" max="5" width="9.7890625" customWidth="1"/>
+    <col min="6" max="6" width="11.3671875" customWidth="1"/>
+    <col min="7" max="7" width="13.3671875" customWidth="1"/>
+    <col min="8" max="8" width="13.15625" customWidth="1"/>
+    <col min="9" max="9" width="15.578125" customWidth="1"/>
+    <col min="10" max="11" width="9.26171875" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="8.83984375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.83984375" customWidth="1"/>
+    <col min="19" max="19" width="11.3671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" ht="23.1" x14ac:dyDescent="0.85">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
     </row>
-    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3463,28 +3482,39 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
     </row>
-    <row r="3" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="16" t="s">
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
       <c r="I3" s="16"/>
       <c r="J3" s="16"/>
       <c r="K3" s="16"/>
       <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
+      <c r="O3" s="16"/>
+      <c r="P3" s="16"/>
+      <c r="Q3" s="16"/>
+      <c r="R3" s="16"/>
+      <c r="S3" s="16"/>
     </row>
-    <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="8"/>
       <c r="B4" s="14" t="s">
         <v>2</v>
@@ -3492,130 +3522,165 @@
       <c r="C4" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="I4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="J4" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="K4" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="L4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="M4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="N4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="O4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="P4" s="8" t="s">
         <v>15</v>
       </c>
+      <c r="Q4" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="R4" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="S4" s="8" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="5" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A5" s="2">
         <v>1881</v>
       </c>
       <c r="B5" s="4">
-        <f>D5 + 100000</f>
+        <f>H5 + 100000</f>
         <v>1100000</v>
       </c>
       <c r="C5" s="9">
         <f>(B5+B6) /2</f>
         <v>1110025</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="4">
         <v>1000000</v>
       </c>
-      <c r="E5" s="4">
-        <f>(D5+D6) /2</f>
+      <c r="I5" s="4">
+        <f>(H5+H6) /2</f>
         <v>1010025</v>
       </c>
-      <c r="F5" s="4">
+      <c r="J5" s="4">
         <v>50000</v>
       </c>
-      <c r="G5" s="4">
+      <c r="K5" s="4">
         <v>30000</v>
       </c>
-      <c r="H5" s="4">
+      <c r="L5" s="4">
         <v>50</v>
       </c>
-      <c r="I5" s="5">
-        <f>F5/E5*1000</f>
+      <c r="M5" s="5">
+        <f>J5/I5*1000</f>
         <v>49.503725155317937</v>
       </c>
-      <c r="J5" s="5">
-        <f>G5/E5*1000</f>
+      <c r="N5" s="5">
+        <f>K5/I5*1000</f>
         <v>29.702235093190762</v>
       </c>
-      <c r="K5" s="10">
-        <f>I5-J5</f>
+      <c r="O5" s="10">
+        <f>M5-N5</f>
         <v>19.801490062127176</v>
       </c>
-      <c r="L5" s="10">
-        <f>E5/C5*100</f>
+      <c r="P5" s="10">
+        <f>I5/C5*100</f>
         <v>90.991193892029457</v>
       </c>
+      <c r="Q5" s="15"/>
+      <c r="R5" s="15"/>
+      <c r="S5" s="15"/>
     </row>
-    <row r="6" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A6" s="2">
         <f>A5+1</f>
         <v>1882</v>
       </c>
       <c r="B6" s="4">
-        <f t="shared" ref="B6:B39" si="0">D6 + 100000</f>
+        <f t="shared" ref="B6:B39" si="0">H6 + 100000</f>
         <v>1120050</v>
       </c>
       <c r="C6" s="9">
         <f t="shared" ref="C6:C38" si="1">(B6+B7) /2</f>
         <v>1130080</v>
       </c>
-      <c r="D6" s="4">
-        <f>D5+F5-G5+H5</f>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="4">
+        <f>H5+J5-K5+L5</f>
         <v>1020050</v>
       </c>
-      <c r="E6" s="4">
-        <f t="shared" ref="E6:E38" si="2">(D6+D7) /2</f>
+      <c r="I6" s="4">
+        <f t="shared" ref="I6:I38" si="2">(H6+H7) /2</f>
         <v>1030080</v>
       </c>
-      <c r="F6" s="4">
-        <f>F5+100</f>
+      <c r="J6" s="4">
+        <f>J5+100</f>
         <v>50100</v>
       </c>
-      <c r="G6" s="4">
-        <f>G5+100</f>
+      <c r="K6" s="4">
+        <f>K5+100</f>
         <v>30100</v>
       </c>
-      <c r="H6" s="4">
-        <f>H5+10</f>
+      <c r="L6" s="4">
+        <f>L5+10</f>
         <v>60</v>
       </c>
-      <c r="I6" s="5">
-        <f t="shared" ref="I6:I38" si="3">F6/E6*1000</f>
+      <c r="M6" s="5">
+        <f t="shared" ref="M6:M38" si="3">J6/I6*1000</f>
         <v>48.636999068033553</v>
       </c>
-      <c r="J6" s="5">
-        <f t="shared" ref="J6:J38" si="4">G6/E6*1000</f>
+      <c r="N6" s="5">
+        <f t="shared" ref="N6:N38" si="4">K6/I6*1000</f>
         <v>29.22103137620379</v>
       </c>
-      <c r="K6" s="10">
-        <f t="shared" ref="K6:K38" si="5">I6-J6</f>
+      <c r="O6" s="10">
+        <f t="shared" ref="O6:O38" si="5">M6-N6</f>
         <v>19.415967691829763</v>
       </c>
-      <c r="L6" s="10">
-        <f t="shared" ref="L6:L38" si="6">E6/C6*100</f>
+      <c r="P6" s="10">
+        <f t="shared" ref="P6:P38" si="6">I6/C6*100</f>
         <v>91.151068950870737</v>
       </c>
+      <c r="Q6" s="15"/>
+      <c r="R6" s="15"/>
+      <c r="S6" s="15"/>
     </row>
-    <row r="7" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A7" s="2">
         <f t="shared" ref="A7:A37" si="7">A6+1</f>
         <v>1883</v>
@@ -3628,44 +3693,51 @@
         <f t="shared" si="1"/>
         <v>1150145</v>
       </c>
-      <c r="D7" s="4">
-        <f t="shared" ref="D7:D39" si="8">D6+F6-G6+H6</f>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="4">
+        <f t="shared" ref="H7:H39" si="8">H6+J6-K6+L6</f>
         <v>1040110</v>
       </c>
-      <c r="E7" s="4">
+      <c r="I7" s="4">
         <f t="shared" si="2"/>
         <v>1050145</v>
       </c>
-      <c r="F7" s="4">
-        <f t="shared" ref="F7:F38" si="9">F6+100</f>
+      <c r="J7" s="4">
+        <f t="shared" ref="J7:J38" si="9">J6+100</f>
         <v>50200</v>
       </c>
-      <c r="G7" s="4">
-        <f t="shared" ref="G7:G38" si="10">G6+100</f>
+      <c r="K7" s="4">
+        <f t="shared" ref="K7:K38" si="10">K6+100</f>
         <v>30200</v>
       </c>
-      <c r="H7" s="4">
-        <f t="shared" ref="H7:H38" si="11">H6+10</f>
+      <c r="L7" s="4">
+        <f t="shared" ref="L7:L38" si="11">L6+10</f>
         <v>70</v>
       </c>
-      <c r="I7" s="5">
+      <c r="M7" s="5">
         <f t="shared" si="3"/>
         <v>47.802922453565941</v>
       </c>
-      <c r="J7" s="5">
+      <c r="N7" s="5">
         <f t="shared" si="4"/>
         <v>28.757933428240861</v>
       </c>
-      <c r="K7" s="10">
+      <c r="O7" s="10">
         <f t="shared" si="5"/>
         <v>19.04498902532508</v>
       </c>
-      <c r="L7" s="10">
+      <c r="P7" s="10">
         <f t="shared" si="6"/>
         <v>91.305444096179173</v>
       </c>
+      <c r="Q7" s="15"/>
+      <c r="R7" s="15"/>
+      <c r="S7" s="15"/>
     </row>
-    <row r="8" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A8" s="2">
         <f t="shared" si="7"/>
         <v>1884</v>
@@ -3678,44 +3750,51 @@
         <f t="shared" si="1"/>
         <v>1170220</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="4">
         <f t="shared" si="8"/>
         <v>1060180</v>
       </c>
-      <c r="E8" s="4">
+      <c r="I8" s="4">
         <f t="shared" si="2"/>
         <v>1070220</v>
       </c>
-      <c r="F8" s="4">
+      <c r="J8" s="4">
         <f t="shared" si="9"/>
         <v>50300</v>
       </c>
-      <c r="G8" s="4">
+      <c r="K8" s="4">
         <f t="shared" si="10"/>
         <v>30300</v>
       </c>
-      <c r="H8" s="4">
+      <c r="L8" s="4">
         <f t="shared" si="11"/>
         <v>80</v>
       </c>
-      <c r="I8" s="5">
+      <c r="M8" s="5">
         <f t="shared" si="3"/>
         <v>46.99968230831044</v>
       </c>
-      <c r="J8" s="5">
+      <c r="N8" s="5">
         <f t="shared" si="4"/>
         <v>28.311935863654202</v>
       </c>
-      <c r="K8" s="10">
+      <c r="O8" s="10">
         <f t="shared" si="5"/>
         <v>18.687746444656238</v>
       </c>
-      <c r="L8" s="10">
+      <c r="P8" s="10">
         <f t="shared" si="6"/>
         <v>91.454598280665181</v>
       </c>
+      <c r="Q8" s="15"/>
+      <c r="R8" s="15"/>
+      <c r="S8" s="15"/>
     </row>
-    <row r="9" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A9" s="2">
         <f t="shared" si="7"/>
         <v>1885</v>
@@ -3728,44 +3807,51 @@
         <f t="shared" si="1"/>
         <v>1190305</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="4">
         <f t="shared" si="8"/>
         <v>1080260</v>
       </c>
-      <c r="E9" s="4">
+      <c r="I9" s="4">
         <f t="shared" si="2"/>
         <v>1090305</v>
       </c>
-      <c r="F9" s="4">
+      <c r="J9" s="4">
         <f t="shared" si="9"/>
         <v>50400</v>
       </c>
-      <c r="G9" s="4">
+      <c r="K9" s="4">
         <f t="shared" si="10"/>
         <v>30400</v>
       </c>
-      <c r="H9" s="4">
+      <c r="L9" s="4">
         <f t="shared" si="11"/>
         <v>90</v>
       </c>
-      <c r="I9" s="5">
+      <c r="M9" s="5">
         <f t="shared" si="3"/>
         <v>46.225597424573856</v>
       </c>
-      <c r="J9" s="5">
+      <c r="N9" s="5">
         <f t="shared" si="4"/>
         <v>27.882106383076298</v>
       </c>
-      <c r="K9" s="10">
+      <c r="O9" s="10">
         <f t="shared" si="5"/>
         <v>18.343491041497558</v>
       </c>
-      <c r="L9" s="10">
+      <c r="P9" s="10">
         <f t="shared" si="6"/>
         <v>91.598791906276119</v>
       </c>
+      <c r="Q9" s="15"/>
+      <c r="R9" s="15"/>
+      <c r="S9" s="15"/>
     </row>
-    <row r="10" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A10" s="2">
         <f t="shared" si="7"/>
         <v>1886</v>
@@ -3778,44 +3864,51 @@
         <f t="shared" si="1"/>
         <v>1210400</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="4">
         <f t="shared" si="8"/>
         <v>1100350</v>
       </c>
-      <c r="E10" s="4">
+      <c r="I10" s="4">
         <f t="shared" si="2"/>
         <v>1110400</v>
       </c>
-      <c r="F10" s="4">
+      <c r="J10" s="4">
         <f t="shared" si="9"/>
         <v>50500</v>
       </c>
-      <c r="G10" s="4">
+      <c r="K10" s="4">
         <f t="shared" si="10"/>
         <v>30500</v>
       </c>
-      <c r="H10" s="4">
+      <c r="L10" s="4">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="I10" s="5">
+      <c r="M10" s="5">
         <f t="shared" si="3"/>
         <v>45.479106628242072</v>
       </c>
-      <c r="J10" s="5">
+      <c r="N10" s="5">
         <f t="shared" si="4"/>
         <v>27.467579250720462</v>
       </c>
-      <c r="K10" s="10">
+      <c r="O10" s="10">
         <f t="shared" si="5"/>
         <v>18.01152737752161</v>
       </c>
-      <c r="L10" s="10">
+      <c r="P10" s="10">
         <f t="shared" si="6"/>
         <v>91.738268341044289</v>
       </c>
+      <c r="Q10" s="15"/>
+      <c r="R10" s="15"/>
+      <c r="S10" s="15"/>
     </row>
-    <row r="11" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A11" s="2">
         <f t="shared" si="7"/>
         <v>1887</v>
@@ -3828,44 +3921,51 @@
         <f t="shared" si="1"/>
         <v>1230505</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="4">
         <f t="shared" si="8"/>
         <v>1120450</v>
       </c>
-      <c r="E11" s="4">
+      <c r="I11" s="4">
         <f t="shared" si="2"/>
         <v>1130505</v>
       </c>
-      <c r="F11" s="4">
+      <c r="J11" s="4">
         <f t="shared" si="9"/>
         <v>50600</v>
       </c>
-      <c r="G11" s="4">
+      <c r="K11" s="4">
         <f t="shared" si="10"/>
         <v>30600</v>
       </c>
-      <c r="H11" s="4">
+      <c r="L11" s="4">
         <f t="shared" si="11"/>
         <v>110</v>
       </c>
-      <c r="I11" s="5">
+      <c r="M11" s="5">
         <f t="shared" si="3"/>
         <v>44.758758254054605</v>
       </c>
-      <c r="J11" s="5">
+      <c r="N11" s="5">
         <f t="shared" si="4"/>
         <v>27.067549457985589</v>
       </c>
-      <c r="K11" s="10">
+      <c r="O11" s="10">
         <f t="shared" si="5"/>
         <v>17.691208796069017</v>
       </c>
-      <c r="L11" s="10">
+      <c r="P11" s="10">
         <f t="shared" si="6"/>
         <v>91.873255289494963</v>
       </c>
+      <c r="Q11" s="15"/>
+      <c r="R11" s="15"/>
+      <c r="S11" s="15"/>
     </row>
-    <row r="12" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A12" s="2">
         <f t="shared" si="7"/>
         <v>1888</v>
@@ -3878,44 +3978,51 @@
         <f t="shared" si="1"/>
         <v>1250620</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="4">
         <f t="shared" si="8"/>
         <v>1140560</v>
       </c>
-      <c r="E12" s="4">
+      <c r="I12" s="4">
         <f t="shared" si="2"/>
         <v>1150620</v>
       </c>
-      <c r="F12" s="4">
+      <c r="J12" s="4">
         <f t="shared" si="9"/>
         <v>50700</v>
       </c>
-      <c r="G12" s="4">
+      <c r="K12" s="4">
         <f t="shared" si="10"/>
         <v>30700</v>
       </c>
-      <c r="H12" s="4">
+      <c r="L12" s="4">
         <f t="shared" si="11"/>
         <v>120</v>
       </c>
-      <c r="I12" s="5">
+      <c r="M12" s="5">
         <f t="shared" si="3"/>
         <v>44.063200709182873</v>
       </c>
-      <c r="J12" s="5">
+      <c r="N12" s="5">
         <f t="shared" si="4"/>
         <v>26.681267490570303</v>
       </c>
-      <c r="K12" s="10">
+      <c r="O12" s="10">
         <f t="shared" si="5"/>
         <v>17.38193321861257</v>
       </c>
-      <c r="L12" s="10">
+      <c r="P12" s="10">
         <f t="shared" si="6"/>
         <v>92.0039660328477</v>
       </c>
+      <c r="Q12" s="15"/>
+      <c r="R12" s="15"/>
+      <c r="S12" s="15"/>
     </row>
-    <row r="13" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A13" s="2">
         <f t="shared" si="7"/>
         <v>1889</v>
@@ -3928,44 +4035,51 @@
         <f t="shared" si="1"/>
         <v>1270745</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="4">
         <f t="shared" si="8"/>
         <v>1160680</v>
       </c>
-      <c r="E13" s="4">
+      <c r="I13" s="4">
         <f t="shared" si="2"/>
         <v>1170745</v>
       </c>
-      <c r="F13" s="4">
+      <c r="J13" s="4">
         <f t="shared" si="9"/>
         <v>50800</v>
       </c>
-      <c r="G13" s="4">
+      <c r="K13" s="4">
         <f t="shared" si="10"/>
         <v>30800</v>
       </c>
-      <c r="H13" s="4">
+      <c r="L13" s="4">
         <f t="shared" si="11"/>
         <v>130</v>
       </c>
-      <c r="I13" s="5">
+      <c r="M13" s="5">
         <f t="shared" si="3"/>
         <v>43.391173996045254</v>
       </c>
-      <c r="J13" s="5">
+      <c r="N13" s="5">
         <f t="shared" si="4"/>
         <v>26.308034627523501</v>
       </c>
-      <c r="K13" s="10">
+      <c r="O13" s="10">
         <f t="shared" si="5"/>
         <v>17.083139368521753</v>
       </c>
-      <c r="L13" s="10">
+      <c r="P13" s="10">
         <f t="shared" si="6"/>
         <v>92.130600553218784</v>
       </c>
+      <c r="Q13" s="15"/>
+      <c r="R13" s="15"/>
+      <c r="S13" s="15"/>
     </row>
-    <row r="14" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A14" s="2">
         <f t="shared" si="7"/>
         <v>1890</v>
@@ -3978,44 +4092,51 @@
         <f t="shared" si="1"/>
         <v>1290880</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="4">
         <f t="shared" si="8"/>
         <v>1180810</v>
       </c>
-      <c r="E14" s="4">
+      <c r="I14" s="4">
         <f t="shared" si="2"/>
         <v>1190880</v>
       </c>
-      <c r="F14" s="4">
+      <c r="J14" s="4">
         <f t="shared" si="9"/>
         <v>50900</v>
       </c>
-      <c r="G14" s="4">
+      <c r="K14" s="4">
         <f t="shared" si="10"/>
         <v>30900</v>
       </c>
-      <c r="H14" s="4">
+      <c r="L14" s="4">
         <f t="shared" si="11"/>
         <v>140</v>
       </c>
-      <c r="I14" s="5">
+      <c r="M14" s="5">
         <f t="shared" si="3"/>
         <v>42.741502082493618</v>
       </c>
-      <c r="J14" s="5">
+      <c r="N14" s="5">
         <f t="shared" si="4"/>
         <v>25.947198710197501</v>
       </c>
-      <c r="K14" s="10">
+      <c r="O14" s="10">
         <f t="shared" si="5"/>
         <v>16.794303372296117</v>
       </c>
-      <c r="L14" s="10">
+      <c r="P14" s="10">
         <f t="shared" si="6"/>
         <v>92.253346554288555</v>
       </c>
+      <c r="Q14" s="15"/>
+      <c r="R14" s="15"/>
+      <c r="S14" s="15"/>
     </row>
-    <row r="15" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A15" s="2">
         <f t="shared" si="7"/>
         <v>1891</v>
@@ -4028,44 +4149,51 @@
         <f t="shared" si="1"/>
         <v>1311025</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="4">
         <f t="shared" si="8"/>
         <v>1200950</v>
       </c>
-      <c r="E15" s="4">
+      <c r="I15" s="4">
         <f t="shared" si="2"/>
         <v>1211025</v>
       </c>
-      <c r="F15" s="4">
+      <c r="J15" s="4">
         <f t="shared" si="9"/>
         <v>51000</v>
       </c>
-      <c r="G15" s="4">
+      <c r="K15" s="4">
         <f t="shared" si="10"/>
         <v>31000</v>
       </c>
-      <c r="H15" s="4">
+      <c r="L15" s="4">
         <f t="shared" si="11"/>
         <v>150</v>
       </c>
-      <c r="I15" s="5">
+      <c r="M15" s="5">
         <f t="shared" si="3"/>
         <v>42.113086022171302</v>
       </c>
-      <c r="J15" s="5">
+      <c r="N15" s="5">
         <f t="shared" si="4"/>
         <v>25.598150327202166</v>
       </c>
-      <c r="K15" s="10">
+      <c r="O15" s="10">
         <f t="shared" si="5"/>
         <v>16.514935694969136</v>
       </c>
-      <c r="L15" s="10">
+      <c r="P15" s="10">
         <f t="shared" si="6"/>
         <v>92.372380389389988</v>
       </c>
+      <c r="Q15" s="15"/>
+      <c r="R15" s="15"/>
+      <c r="S15" s="15"/>
     </row>
-    <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A16" s="2">
         <f t="shared" si="7"/>
         <v>1892</v>
@@ -4078,44 +4206,51 @@
         <f t="shared" si="1"/>
         <v>1331180</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="4">
         <f t="shared" si="8"/>
         <v>1221100</v>
       </c>
-      <c r="E16" s="4">
+      <c r="I16" s="4">
         <f t="shared" si="2"/>
         <v>1231180</v>
       </c>
-      <c r="F16" s="4">
+      <c r="J16" s="4">
         <f t="shared" si="9"/>
         <v>51100</v>
       </c>
-      <c r="G16" s="4">
+      <c r="K16" s="4">
         <f t="shared" si="10"/>
         <v>31100</v>
       </c>
-      <c r="H16" s="4">
+      <c r="L16" s="4">
         <f t="shared" si="11"/>
         <v>160</v>
       </c>
-      <c r="I16" s="5">
+      <c r="M16" s="5">
         <f t="shared" si="3"/>
         <v>41.504897740379143</v>
       </c>
-      <c r="J16" s="5">
+      <c r="N16" s="5">
         <f t="shared" si="4"/>
         <v>25.260319368410791</v>
       </c>
-      <c r="K16" s="10">
+      <c r="O16" s="10">
         <f t="shared" si="5"/>
         <v>16.244578371968352</v>
       </c>
-      <c r="L16" s="10">
+      <c r="P16" s="10">
         <f t="shared" si="6"/>
         <v>92.48786790666928</v>
       </c>
+      <c r="Q16" s="15"/>
+      <c r="R16" s="15"/>
+      <c r="S16" s="15"/>
     </row>
-    <row r="17" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A17" s="2">
         <f t="shared" si="7"/>
         <v>1893</v>
@@ -4128,44 +4263,51 @@
         <f t="shared" si="1"/>
         <v>1351345</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="4">
         <f t="shared" si="8"/>
         <v>1241260</v>
       </c>
-      <c r="E17" s="4">
+      <c r="I17" s="4">
         <f t="shared" si="2"/>
         <v>1251345</v>
       </c>
-      <c r="F17" s="4">
+      <c r="J17" s="4">
         <f t="shared" si="9"/>
         <v>51200</v>
       </c>
-      <c r="G17" s="4">
+      <c r="K17" s="4">
         <f t="shared" si="10"/>
         <v>31200</v>
       </c>
-      <c r="H17" s="4">
+      <c r="L17" s="4">
         <f t="shared" si="11"/>
         <v>170</v>
       </c>
-      <c r="I17" s="5">
+      <c r="M17" s="5">
         <f t="shared" si="3"/>
         <v>40.915974411533192</v>
       </c>
-      <c r="J17" s="5">
+      <c r="N17" s="5">
         <f t="shared" si="4"/>
         <v>24.933171907028036</v>
       </c>
-      <c r="K17" s="10">
+      <c r="O17" s="10">
         <f t="shared" si="5"/>
         <v>15.982802504505155</v>
       </c>
-      <c r="L17" s="10">
+      <c r="P17" s="10">
         <f t="shared" si="6"/>
         <v>92.599965219836534</v>
       </c>
+      <c r="Q17" s="15"/>
+      <c r="R17" s="15"/>
+      <c r="S17" s="15"/>
     </row>
-    <row r="18" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A18" s="2">
         <f t="shared" si="7"/>
         <v>1894</v>
@@ -4178,44 +4320,51 @@
         <f t="shared" si="1"/>
         <v>1371520</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="4">
         <f t="shared" si="8"/>
         <v>1261430</v>
       </c>
-      <c r="E18" s="4">
+      <c r="I18" s="4">
         <f t="shared" si="2"/>
         <v>1271520</v>
       </c>
-      <c r="F18" s="4">
+      <c r="J18" s="4">
         <f t="shared" si="9"/>
         <v>51300</v>
       </c>
-      <c r="G18" s="4">
+      <c r="K18" s="4">
         <f t="shared" si="10"/>
         <v>31300</v>
       </c>
-      <c r="H18" s="4">
+      <c r="L18" s="4">
         <f t="shared" si="11"/>
         <v>180</v>
       </c>
-      <c r="I18" s="5">
+      <c r="M18" s="5">
         <f t="shared" si="3"/>
         <v>40.34541336353341</v>
       </c>
-      <c r="J18" s="5">
+      <c r="N18" s="5">
         <f t="shared" si="4"/>
         <v>24.616207373851765</v>
       </c>
-      <c r="K18" s="10">
+      <c r="O18" s="10">
         <f t="shared" si="5"/>
         <v>15.729205989681645</v>
       </c>
-      <c r="L18" s="10">
+      <c r="P18" s="10">
         <f t="shared" si="6"/>
         <v>92.708819412039205</v>
       </c>
+      <c r="Q18" s="15"/>
+      <c r="R18" s="15"/>
+      <c r="S18" s="15"/>
     </row>
-    <row r="19" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A19" s="2">
         <f t="shared" si="7"/>
         <v>1895</v>
@@ -4228,44 +4377,51 @@
         <f t="shared" si="1"/>
         <v>1391705</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="4">
         <f t="shared" si="8"/>
         <v>1281610</v>
       </c>
-      <c r="E19" s="4">
+      <c r="I19" s="4">
         <f t="shared" si="2"/>
         <v>1291705</v>
       </c>
-      <c r="F19" s="4">
+      <c r="J19" s="4">
         <f t="shared" si="9"/>
         <v>51400</v>
       </c>
-      <c r="G19" s="4">
+      <c r="K19" s="4">
         <f t="shared" si="10"/>
         <v>31400</v>
       </c>
-      <c r="H19" s="4">
+      <c r="L19" s="4">
         <f t="shared" si="11"/>
         <v>190</v>
       </c>
-      <c r="I19" s="5">
+      <c r="M19" s="5">
         <f t="shared" si="3"/>
         <v>39.792367452320775</v>
       </c>
-      <c r="J19" s="5">
+      <c r="N19" s="5">
         <f t="shared" si="4"/>
         <v>24.308955992273777</v>
       </c>
-      <c r="K19" s="10">
+      <c r="O19" s="10">
         <f t="shared" si="5"/>
         <v>15.483411460046998</v>
       </c>
-      <c r="L19" s="10">
+      <c r="P19" s="10">
         <f t="shared" si="6"/>
         <v>92.814569179531574</v>
       </c>
+      <c r="Q19" s="15"/>
+      <c r="R19" s="15"/>
+      <c r="S19" s="15"/>
     </row>
-    <row r="20" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A20" s="2">
         <f t="shared" si="7"/>
         <v>1896</v>
@@ -4278,44 +4434,51 @@
         <f t="shared" si="1"/>
         <v>1411900</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="4">
         <f t="shared" si="8"/>
         <v>1301800</v>
       </c>
-      <c r="E20" s="4">
+      <c r="I20" s="4">
         <f t="shared" si="2"/>
         <v>1311900</v>
       </c>
-      <c r="F20" s="4">
+      <c r="J20" s="4">
         <f t="shared" si="9"/>
         <v>51500</v>
       </c>
-      <c r="G20" s="4">
+      <c r="K20" s="4">
         <f t="shared" si="10"/>
         <v>31500</v>
       </c>
-      <c r="H20" s="4">
+      <c r="L20" s="4">
         <f t="shared" si="11"/>
         <v>200</v>
       </c>
-      <c r="I20" s="5">
+      <c r="M20" s="5">
         <f t="shared" si="3"/>
         <v>39.256040856772614</v>
       </c>
-      <c r="J20" s="5">
+      <c r="N20" s="5">
         <f t="shared" si="4"/>
         <v>24.010976446375484</v>
       </c>
-      <c r="K20" s="10">
+      <c r="O20" s="10">
         <f t="shared" si="5"/>
         <v>15.245064410397131</v>
       </c>
-      <c r="L20" s="10">
+      <c r="P20" s="10">
         <f t="shared" si="6"/>
         <v>92.917345421063814</v>
       </c>
+      <c r="Q20" s="15"/>
+      <c r="R20" s="15"/>
+      <c r="S20" s="15"/>
     </row>
-    <row r="21" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A21" s="2">
         <f t="shared" si="7"/>
         <v>1897</v>
@@ -4328,44 +4491,51 @@
         <f t="shared" si="1"/>
         <v>1432105</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="4">
         <f t="shared" si="8"/>
         <v>1322000</v>
       </c>
-      <c r="E21" s="4">
+      <c r="I21" s="4">
         <f t="shared" si="2"/>
         <v>1332105</v>
       </c>
-      <c r="F21" s="4">
+      <c r="J21" s="4">
         <f t="shared" si="9"/>
         <v>51600</v>
       </c>
-      <c r="G21" s="4">
+      <c r="K21" s="4">
         <f t="shared" si="10"/>
         <v>31600</v>
       </c>
-      <c r="H21" s="4">
+      <c r="L21" s="4">
         <f t="shared" si="11"/>
         <v>210</v>
       </c>
-      <c r="I21" s="5">
+      <c r="M21" s="5">
         <f t="shared" si="3"/>
         <v>38.735685250036596</v>
       </c>
-      <c r="J21" s="5">
+      <c r="N21" s="5">
         <f t="shared" si="4"/>
         <v>23.721853757774351</v>
       </c>
-      <c r="K21" s="10">
+      <c r="O21" s="10">
         <f t="shared" si="5"/>
         <v>15.013831492262245</v>
       </c>
-      <c r="L21" s="10">
+      <c r="P21" s="10">
         <f t="shared" si="6"/>
         <v>93.017271778256486</v>
       </c>
+      <c r="Q21" s="15"/>
+      <c r="R21" s="15"/>
+      <c r="S21" s="15"/>
     </row>
-    <row r="22" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A22" s="2">
         <f t="shared" si="7"/>
         <v>1898</v>
@@ -4378,44 +4548,51 @@
         <f t="shared" si="1"/>
         <v>1452320</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="4">
         <f t="shared" si="8"/>
         <v>1342210</v>
       </c>
-      <c r="E22" s="4">
+      <c r="I22" s="4">
         <f t="shared" si="2"/>
         <v>1352320</v>
       </c>
-      <c r="F22" s="4">
+      <c r="J22" s="4">
         <f t="shared" si="9"/>
         <v>51700</v>
       </c>
-      <c r="G22" s="4">
+      <c r="K22" s="4">
         <f t="shared" si="10"/>
         <v>31700</v>
       </c>
-      <c r="H22" s="4">
+      <c r="L22" s="4">
         <f t="shared" si="11"/>
         <v>220</v>
       </c>
-      <c r="I22" s="5">
+      <c r="M22" s="5">
         <f t="shared" si="3"/>
         <v>38.230596308566021</v>
       </c>
-      <c r="J22" s="5">
+      <c r="N22" s="5">
         <f t="shared" si="4"/>
         <v>23.441197349739706</v>
       </c>
-      <c r="K22" s="10">
+      <c r="O22" s="10">
         <f t="shared" si="5"/>
         <v>14.789398958826315</v>
       </c>
-      <c r="L22" s="10">
+      <c r="P22" s="10">
         <f t="shared" si="6"/>
         <v>93.114465131651428</v>
       </c>
+      <c r="Q22" s="15"/>
+      <c r="R22" s="15"/>
+      <c r="S22" s="15"/>
     </row>
-    <row r="23" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A23" s="2">
         <f t="shared" si="7"/>
         <v>1899</v>
@@ -4428,44 +4605,51 @@
         <f t="shared" si="1"/>
         <v>1472545</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="4">
         <f t="shared" si="8"/>
         <v>1362430</v>
       </c>
-      <c r="E23" s="4">
+      <c r="I23" s="4">
         <f t="shared" si="2"/>
         <v>1372545</v>
       </c>
-      <c r="F23" s="4">
+      <c r="J23" s="4">
         <f t="shared" si="9"/>
         <v>51800</v>
       </c>
-      <c r="G23" s="4">
+      <c r="K23" s="4">
         <f t="shared" si="10"/>
         <v>31800</v>
       </c>
-      <c r="H23" s="4">
+      <c r="L23" s="4">
         <f t="shared" si="11"/>
         <v>230</v>
       </c>
-      <c r="I23" s="5">
+      <c r="M23" s="5">
         <f t="shared" si="3"/>
         <v>37.740110524609392</v>
       </c>
-      <c r="J23" s="5">
+      <c r="N23" s="5">
         <f t="shared" si="4"/>
         <v>23.168639279586461</v>
       </c>
-      <c r="K23" s="10">
+      <c r="O23" s="10">
         <f t="shared" si="5"/>
         <v>14.571471245022931</v>
       </c>
-      <c r="L23" s="10">
+      <c r="P23" s="10">
         <f t="shared" si="6"/>
         <v>93.209036056623063</v>
       </c>
+      <c r="Q23" s="15"/>
+      <c r="R23" s="15"/>
+      <c r="S23" s="15"/>
     </row>
-    <row r="24" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A24" s="2">
         <f t="shared" si="7"/>
         <v>1900</v>
@@ -4478,44 +4662,51 @@
         <f t="shared" si="1"/>
         <v>1492780</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="4">
         <f t="shared" si="8"/>
         <v>1382660</v>
       </c>
-      <c r="E24" s="4">
+      <c r="I24" s="4">
         <f t="shared" si="2"/>
         <v>1392780</v>
       </c>
-      <c r="F24" s="4">
+      <c r="J24" s="4">
         <f t="shared" si="9"/>
         <v>51900</v>
       </c>
-      <c r="G24" s="4">
+      <c r="K24" s="4">
         <f t="shared" si="10"/>
         <v>31900</v>
       </c>
-      <c r="H24" s="4">
+      <c r="L24" s="4">
         <f t="shared" si="11"/>
         <v>240</v>
       </c>
-      <c r="I24" s="5">
+      <c r="M24" s="5">
         <f t="shared" si="3"/>
         <v>37.26360229181924</v>
       </c>
-      <c r="J24" s="5">
+      <c r="N24" s="5">
         <f t="shared" si="4"/>
         <v>22.903832622524735</v>
       </c>
-      <c r="K24" s="10">
+      <c r="O24" s="10">
         <f t="shared" si="5"/>
         <v>14.359769669294504</v>
       </c>
-      <c r="L24" s="10">
+      <c r="P24" s="10">
         <f t="shared" si="6"/>
         <v>93.301089242889105</v>
       </c>
+      <c r="Q24" s="15"/>
+      <c r="R24" s="15"/>
+      <c r="S24" s="15"/>
     </row>
-    <row r="25" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A25" s="2">
         <f t="shared" si="7"/>
         <v>1901</v>
@@ -4528,44 +4719,51 @@
         <f t="shared" si="1"/>
         <v>1513025</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="4">
         <f t="shared" si="8"/>
         <v>1402900</v>
       </c>
-      <c r="E25" s="4">
+      <c r="I25" s="4">
         <f t="shared" si="2"/>
         <v>1413025</v>
       </c>
-      <c r="F25" s="4">
+      <c r="J25" s="4">
         <f t="shared" si="9"/>
         <v>52000</v>
       </c>
-      <c r="G25" s="4">
+      <c r="K25" s="4">
         <f t="shared" si="10"/>
         <v>32000</v>
       </c>
-      <c r="H25" s="4">
+      <c r="L25" s="4">
         <f t="shared" si="11"/>
         <v>250</v>
       </c>
-      <c r="I25" s="5">
+      <c r="M25" s="5">
         <f t="shared" si="3"/>
         <v>36.800481237062328</v>
       </c>
-      <c r="J25" s="5">
+      <c r="N25" s="5">
         <f t="shared" si="4"/>
         <v>22.646449992038356</v>
       </c>
-      <c r="K25" s="10">
+      <c r="O25" s="10">
         <f t="shared" si="5"/>
         <v>14.154031245023972</v>
       </c>
-      <c r="L25" s="10">
+      <c r="P25" s="10">
         <f t="shared" si="6"/>
         <v>93.390723880966945</v>
       </c>
+      <c r="Q25" s="15"/>
+      <c r="R25" s="15"/>
+      <c r="S25" s="15"/>
     </row>
-    <row r="26" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A26" s="2">
         <f t="shared" si="7"/>
         <v>1902</v>
@@ -4578,44 +4776,51 @@
         <f t="shared" si="1"/>
         <v>1533280</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="4">
         <f t="shared" si="8"/>
         <v>1423150</v>
       </c>
-      <c r="E26" s="4">
+      <c r="I26" s="4">
         <f t="shared" si="2"/>
         <v>1433280</v>
       </c>
-      <c r="F26" s="4">
+      <c r="J26" s="4">
         <f t="shared" si="9"/>
         <v>52100</v>
       </c>
-      <c r="G26" s="4">
+      <c r="K26" s="4">
         <f t="shared" si="10"/>
         <v>32100</v>
       </c>
-      <c r="H26" s="4">
+      <c r="L26" s="4">
         <f t="shared" si="11"/>
         <v>260</v>
       </c>
-      <c r="I26" s="5">
+      <c r="M26" s="5">
         <f t="shared" si="3"/>
         <v>36.350189774503235</v>
       </c>
-      <c r="J26" s="5">
+      <c r="N26" s="5">
         <f t="shared" si="4"/>
         <v>22.396182183523106</v>
       </c>
-      <c r="K26" s="10">
+      <c r="O26" s="10">
         <f t="shared" si="5"/>
         <v>13.95400759098013</v>
       </c>
-      <c r="L26" s="10">
+      <c r="P26" s="10">
         <f t="shared" si="6"/>
         <v>93.478034018574562</v>
       </c>
+      <c r="Q26" s="15"/>
+      <c r="R26" s="15"/>
+      <c r="S26" s="15"/>
     </row>
-    <row r="27" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A27" s="2">
         <f t="shared" si="7"/>
         <v>1903</v>
@@ -4628,44 +4833,51 @@
         <f t="shared" si="1"/>
         <v>1553545</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="4">
         <f t="shared" si="8"/>
         <v>1443410</v>
       </c>
-      <c r="E27" s="4">
+      <c r="I27" s="4">
         <f t="shared" si="2"/>
         <v>1453545</v>
       </c>
-      <c r="F27" s="4">
+      <c r="J27" s="4">
         <f t="shared" si="9"/>
         <v>52200</v>
       </c>
-      <c r="G27" s="4">
+      <c r="K27" s="4">
         <f t="shared" si="10"/>
         <v>32200</v>
       </c>
-      <c r="H27" s="4">
+      <c r="L27" s="4">
         <f t="shared" si="11"/>
         <v>270</v>
       </c>
-      <c r="I27" s="5">
+      <c r="M27" s="5">
         <f t="shared" si="3"/>
         <v>35.912200860654472</v>
       </c>
-      <c r="J27" s="5">
+      <c r="N27" s="5">
         <f t="shared" si="4"/>
         <v>22.15273692936923</v>
       </c>
-      <c r="K27" s="10">
+      <c r="O27" s="10">
         <f t="shared" si="5"/>
         <v>13.759463931285243</v>
       </c>
-      <c r="L27" s="10">
+      <c r="P27" s="10">
         <f t="shared" si="6"/>
         <v>93.56310888966847</v>
       </c>
+      <c r="Q27" s="15"/>
+      <c r="R27" s="15"/>
+      <c r="S27" s="15"/>
     </row>
-    <row r="28" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A28" s="2">
         <f t="shared" si="7"/>
         <v>1904</v>
@@ -4678,44 +4890,51 @@
         <f t="shared" si="1"/>
         <v>1573820</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="4">
         <f t="shared" si="8"/>
         <v>1463680</v>
       </c>
-      <c r="E28" s="4">
+      <c r="I28" s="4">
         <f t="shared" si="2"/>
         <v>1473820</v>
       </c>
-      <c r="F28" s="4">
+      <c r="J28" s="4">
         <f t="shared" si="9"/>
         <v>52300</v>
       </c>
-      <c r="G28" s="4">
+      <c r="K28" s="4">
         <f t="shared" si="10"/>
         <v>32300</v>
       </c>
-      <c r="H28" s="4">
+      <c r="L28" s="4">
         <f t="shared" si="11"/>
         <v>280</v>
       </c>
-      <c r="I28" s="5">
+      <c r="M28" s="5">
         <f t="shared" si="3"/>
         <v>35.486015931389176</v>
       </c>
-      <c r="J28" s="5">
+      <c r="N28" s="5">
         <f t="shared" si="4"/>
         <v>21.91583775494972</v>
       </c>
-      <c r="K28" s="10">
+      <c r="O28" s="10">
         <f t="shared" si="5"/>
         <v>13.570178176439455</v>
       </c>
-      <c r="L28" s="10">
+      <c r="P28" s="10">
         <f t="shared" si="6"/>
         <v>93.646033218538335</v>
       </c>
+      <c r="Q28" s="15"/>
+      <c r="R28" s="15"/>
+      <c r="S28" s="15"/>
     </row>
-    <row r="29" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A29" s="2">
         <f t="shared" si="7"/>
         <v>1905</v>
@@ -4728,44 +4947,51 @@
         <f t="shared" si="1"/>
         <v>1594105</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="4">
         <f t="shared" si="8"/>
         <v>1483960</v>
       </c>
-      <c r="E29" s="4">
+      <c r="I29" s="4">
         <f t="shared" si="2"/>
         <v>1494105</v>
       </c>
-      <c r="F29" s="4">
+      <c r="J29" s="4">
         <f t="shared" si="9"/>
         <v>52400</v>
       </c>
-      <c r="G29" s="4">
+      <c r="K29" s="4">
         <f t="shared" si="10"/>
         <v>32400</v>
       </c>
-      <c r="H29" s="4">
+      <c r="L29" s="4">
         <f t="shared" si="11"/>
         <v>290</v>
       </c>
-      <c r="I29" s="5">
+      <c r="M29" s="5">
         <f t="shared" si="3"/>
         <v>35.071163003938807</v>
       </c>
-      <c r="J29" s="5">
+      <c r="N29" s="5">
         <f t="shared" si="4"/>
         <v>21.685222926099573</v>
       </c>
-      <c r="K29" s="10">
+      <c r="O29" s="10">
         <f t="shared" si="5"/>
         <v>13.385940077839233</v>
       </c>
-      <c r="L29" s="10">
+      <c r="P29" s="10">
         <f t="shared" si="6"/>
         <v>93.726887501137</v>
       </c>
+      <c r="Q29" s="15"/>
+      <c r="R29" s="15"/>
+      <c r="S29" s="15"/>
     </row>
-    <row r="30" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A30" s="2">
         <f t="shared" si="7"/>
         <v>1906</v>
@@ -4778,44 +5004,51 @@
         <f t="shared" si="1"/>
         <v>1614400</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="4">
         <f t="shared" si="8"/>
         <v>1504250</v>
       </c>
-      <c r="E30" s="4">
+      <c r="I30" s="4">
         <f t="shared" si="2"/>
         <v>1514400</v>
       </c>
-      <c r="F30" s="4">
+      <c r="J30" s="4">
         <f t="shared" si="9"/>
         <v>52500</v>
       </c>
-      <c r="G30" s="4">
+      <c r="K30" s="4">
         <f t="shared" si="10"/>
         <v>32500</v>
       </c>
-      <c r="H30" s="4">
+      <c r="L30" s="4">
         <f t="shared" si="11"/>
         <v>300</v>
       </c>
-      <c r="I30" s="5">
+      <c r="M30" s="5">
         <f t="shared" si="3"/>
         <v>34.66719492868463</v>
       </c>
-      <c r="J30" s="5">
+      <c r="N30" s="5">
         <f t="shared" si="4"/>
         <v>21.460644479661912</v>
       </c>
-      <c r="K30" s="10">
+      <c r="O30" s="10">
         <f t="shared" si="5"/>
         <v>13.206550449022718</v>
       </c>
-      <c r="L30" s="10">
+      <c r="P30" s="10">
         <f t="shared" si="6"/>
         <v>93.805748265609509</v>
       </c>
+      <c r="Q30" s="15"/>
+      <c r="R30" s="15"/>
+      <c r="S30" s="15"/>
     </row>
-    <row r="31" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A31" s="2">
         <f t="shared" si="7"/>
         <v>1907</v>
@@ -4828,44 +5061,51 @@
         <f t="shared" si="1"/>
         <v>1634705</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="4">
         <f t="shared" si="8"/>
         <v>1524550</v>
       </c>
-      <c r="E31" s="4">
+      <c r="I31" s="4">
         <f t="shared" si="2"/>
         <v>1534705</v>
       </c>
-      <c r="F31" s="4">
+      <c r="J31" s="4">
         <f t="shared" si="9"/>
         <v>52600</v>
       </c>
-      <c r="G31" s="4">
+      <c r="K31" s="4">
         <f t="shared" si="10"/>
         <v>32600</v>
       </c>
-      <c r="H31" s="4">
+      <c r="L31" s="4">
         <f t="shared" si="11"/>
         <v>310</v>
       </c>
-      <c r="I31" s="5">
+      <c r="M31" s="5">
         <f t="shared" si="3"/>
         <v>34.273687777129808</v>
       </c>
-      <c r="J31" s="5">
+      <c r="N31" s="5">
         <f t="shared" si="4"/>
         <v>21.241867329551933</v>
       </c>
-      <c r="K31" s="10">
+      <c r="O31" s="10">
         <f t="shared" si="5"/>
         <v>13.031820447577875</v>
       </c>
-      <c r="L31" s="10">
+      <c r="P31" s="10">
         <f t="shared" si="6"/>
         <v>93.882688313793622</v>
       </c>
+      <c r="Q31" s="15"/>
+      <c r="R31" s="15"/>
+      <c r="S31" s="15"/>
     </row>
-    <row r="32" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A32" s="2">
         <f t="shared" si="7"/>
         <v>1908</v>
@@ -4878,44 +5118,51 @@
         <f t="shared" si="1"/>
         <v>1655020</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="4">
         <f t="shared" si="8"/>
         <v>1544860</v>
       </c>
-      <c r="E32" s="4">
+      <c r="I32" s="4">
         <f t="shared" si="2"/>
         <v>1555020</v>
       </c>
-      <c r="F32" s="4">
+      <c r="J32" s="4">
         <f t="shared" si="9"/>
         <v>52700</v>
       </c>
-      <c r="G32" s="4">
+      <c r="K32" s="4">
         <f t="shared" si="10"/>
         <v>32700</v>
       </c>
-      <c r="H32" s="4">
+      <c r="L32" s="4">
         <f t="shared" si="11"/>
         <v>320</v>
       </c>
-      <c r="I32" s="5">
+      <c r="M32" s="5">
         <f t="shared" si="3"/>
         <v>33.89023935383468</v>
       </c>
-      <c r="J32" s="5">
+      <c r="N32" s="5">
         <f t="shared" si="4"/>
         <v>21.028668441563454</v>
       </c>
-      <c r="K32" s="10">
+      <c r="O32" s="10">
         <f t="shared" si="5"/>
         <v>12.861570912271226</v>
       </c>
-      <c r="L32" s="10">
+      <c r="P32" s="10">
         <f t="shared" si="6"/>
         <v>93.957776945293716</v>
       </c>
+      <c r="Q32" s="15"/>
+      <c r="R32" s="15"/>
+      <c r="S32" s="15"/>
     </row>
-    <row r="33" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A33" s="2">
         <f t="shared" si="7"/>
         <v>1909</v>
@@ -4928,44 +5175,51 @@
         <f t="shared" si="1"/>
         <v>1675345</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="4">
         <f t="shared" si="8"/>
         <v>1565180</v>
       </c>
-      <c r="E33" s="4">
+      <c r="I33" s="4">
         <f t="shared" si="2"/>
         <v>1575345</v>
       </c>
-      <c r="F33" s="4">
+      <c r="J33" s="4">
         <f t="shared" si="9"/>
         <v>52800</v>
       </c>
-      <c r="G33" s="4">
+      <c r="K33" s="4">
         <f t="shared" si="10"/>
         <v>32800</v>
       </c>
-      <c r="H33" s="4">
+      <c r="L33" s="4">
         <f t="shared" si="11"/>
         <v>330</v>
       </c>
-      <c r="I33" s="5">
+      <c r="M33" s="5">
         <f t="shared" si="3"/>
         <v>33.516467821334373</v>
       </c>
-      <c r="J33" s="5">
+      <c r="N33" s="5">
         <f t="shared" si="4"/>
         <v>20.820836070828928</v>
       </c>
-      <c r="K33" s="10">
+      <c r="O33" s="10">
         <f t="shared" si="5"/>
         <v>12.695631750505445</v>
       </c>
-      <c r="L33" s="10">
+      <c r="P33" s="10">
         <f t="shared" si="6"/>
         <v>94.031080165577833</v>
       </c>
+      <c r="Q33" s="15"/>
+      <c r="R33" s="15"/>
+      <c r="S33" s="15"/>
     </row>
-    <row r="34" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A34" s="2">
         <f t="shared" si="7"/>
         <v>1910</v>
@@ -4978,44 +5232,51 @@
         <f t="shared" si="1"/>
         <v>1695680</v>
       </c>
-      <c r="D34" s="4">
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="4">
         <f t="shared" si="8"/>
         <v>1585510</v>
       </c>
-      <c r="E34" s="4">
+      <c r="I34" s="4">
         <f t="shared" si="2"/>
         <v>1595680</v>
       </c>
-      <c r="F34" s="4">
+      <c r="J34" s="4">
         <f t="shared" si="9"/>
         <v>52900</v>
       </c>
-      <c r="G34" s="4">
+      <c r="K34" s="4">
         <f t="shared" si="10"/>
         <v>32900</v>
       </c>
-      <c r="H34" s="4">
+      <c r="L34" s="4">
         <f t="shared" si="11"/>
         <v>340</v>
       </c>
-      <c r="I34" s="5">
+      <c r="M34" s="5">
         <f t="shared" si="3"/>
         <v>33.152010428156018</v>
       </c>
-      <c r="J34" s="5">
+      <c r="N34" s="5">
         <f t="shared" si="4"/>
         <v>20.61816905645242</v>
       </c>
-      <c r="K34" s="10">
+      <c r="O34" s="10">
         <f t="shared" si="5"/>
         <v>12.533841371703598</v>
       </c>
-      <c r="L34" s="10">
+      <c r="P34" s="10">
         <f t="shared" si="6"/>
         <v>94.102660879411218</v>
       </c>
+      <c r="Q34" s="15"/>
+      <c r="R34" s="15"/>
+      <c r="S34" s="15"/>
     </row>
-    <row r="35" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A35" s="2">
         <f t="shared" si="7"/>
         <v>1911</v>
@@ -5028,44 +5289,51 @@
         <f t="shared" si="1"/>
         <v>1716025</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="4">
         <f t="shared" si="8"/>
         <v>1605850</v>
       </c>
-      <c r="E35" s="4">
+      <c r="I35" s="4">
         <f t="shared" si="2"/>
         <v>1616025</v>
       </c>
-      <c r="F35" s="4">
+      <c r="J35" s="4">
         <f t="shared" si="9"/>
         <v>53000</v>
       </c>
-      <c r="G35" s="4">
+      <c r="K35" s="4">
         <f t="shared" si="10"/>
         <v>33000</v>
       </c>
-      <c r="H35" s="4">
+      <c r="L35" s="4">
         <f t="shared" si="11"/>
         <v>350</v>
       </c>
-      <c r="I35" s="5">
+      <c r="M35" s="5">
         <f t="shared" si="3"/>
         <v>32.796522331028299</v>
       </c>
-      <c r="J35" s="5">
+      <c r="N35" s="5">
         <f t="shared" si="4"/>
         <v>20.420476168376108</v>
       </c>
-      <c r="K35" s="10">
+      <c r="O35" s="10">
         <f t="shared" si="5"/>
         <v>12.376046162652191</v>
       </c>
-      <c r="L35" s="10">
+      <c r="P35" s="10">
         <f t="shared" si="6"/>
         <v>94.172579070817733</v>
       </c>
+      <c r="Q35" s="15"/>
+      <c r="R35" s="15"/>
+      <c r="S35" s="15"/>
     </row>
-    <row r="36" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A36" s="2">
         <f t="shared" si="7"/>
         <v>1912</v>
@@ -5078,44 +5346,51 @@
         <f t="shared" si="1"/>
         <v>1736380</v>
       </c>
-      <c r="D36" s="4">
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="4">
         <f t="shared" si="8"/>
         <v>1626200</v>
       </c>
-      <c r="E36" s="4">
+      <c r="I36" s="4">
         <f t="shared" si="2"/>
         <v>1636380</v>
       </c>
-      <c r="F36" s="4">
+      <c r="J36" s="4">
         <f t="shared" si="9"/>
         <v>53100</v>
       </c>
-      <c r="G36" s="4">
+      <c r="K36" s="4">
         <f t="shared" si="10"/>
         <v>33100</v>
       </c>
-      <c r="H36" s="4">
+      <c r="L36" s="4">
         <f t="shared" si="11"/>
         <v>360</v>
       </c>
-      <c r="I36" s="5">
+      <c r="M36" s="5">
         <f t="shared" si="3"/>
         <v>32.449675503244968</v>
       </c>
-      <c r="J36" s="5">
+      <c r="N36" s="5">
         <f t="shared" si="4"/>
         <v>20.227575502022759</v>
       </c>
-      <c r="K36" s="10">
+      <c r="O36" s="10">
         <f t="shared" si="5"/>
         <v>12.222100001222209</v>
       </c>
-      <c r="L36" s="10">
+      <c r="P36" s="10">
         <f t="shared" si="6"/>
         <v>94.240891970651589</v>
       </c>
+      <c r="Q36" s="15"/>
+      <c r="R36" s="15"/>
+      <c r="S36" s="15"/>
     </row>
-    <row r="37" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A37" s="2">
         <f t="shared" si="7"/>
         <v>1913</v>
@@ -5128,44 +5403,51 @@
         <f t="shared" si="1"/>
         <v>1756745</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="4">
         <f t="shared" si="8"/>
         <v>1646560</v>
       </c>
-      <c r="E37" s="4">
+      <c r="I37" s="4">
         <f t="shared" si="2"/>
         <v>1656745</v>
       </c>
-      <c r="F37" s="4">
+      <c r="J37" s="4">
         <f t="shared" si="9"/>
         <v>53200</v>
       </c>
-      <c r="G37" s="4">
+      <c r="K37" s="4">
         <f t="shared" si="10"/>
         <v>33200</v>
       </c>
-      <c r="H37" s="4">
+      <c r="L37" s="4">
         <f t="shared" si="11"/>
         <v>370</v>
       </c>
-      <c r="I37" s="5">
+      <c r="M37" s="5">
         <f t="shared" si="3"/>
         <v>32.11115772191858</v>
       </c>
-      <c r="J37" s="5">
+      <c r="N37" s="5">
         <f t="shared" si="4"/>
         <v>20.039293916686031</v>
       </c>
-      <c r="K37" s="10">
+      <c r="O37" s="10">
         <f t="shared" si="5"/>
         <v>12.07186380523255</v>
       </c>
-      <c r="L37" s="10">
+      <c r="P37" s="10">
         <f t="shared" si="6"/>
         <v>94.307654212762799</v>
       </c>
+      <c r="Q37" s="15"/>
+      <c r="R37" s="15"/>
+      <c r="S37" s="15"/>
     </row>
-    <row r="38" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A38" s="2">
         <f>A37+1</f>
         <v>1914</v>
@@ -5178,44 +5460,51 @@
         <f t="shared" si="1"/>
         <v>1777120</v>
       </c>
-      <c r="D38" s="4">
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="4">
         <f t="shared" si="8"/>
         <v>1666930</v>
       </c>
-      <c r="E38" s="4">
+      <c r="I38" s="4">
         <f t="shared" si="2"/>
         <v>1677120</v>
       </c>
-      <c r="F38" s="4">
+      <c r="J38" s="4">
         <f t="shared" si="9"/>
         <v>53300</v>
       </c>
-      <c r="G38" s="4">
+      <c r="K38" s="4">
         <f t="shared" si="10"/>
         <v>33300</v>
       </c>
-      <c r="H38" s="4">
+      <c r="L38" s="4">
         <f t="shared" si="11"/>
         <v>380</v>
       </c>
-      <c r="I38" s="5">
+      <c r="M38" s="5">
         <f t="shared" si="3"/>
         <v>31.780671627551992</v>
       </c>
-      <c r="J38" s="5">
+      <c r="N38" s="5">
         <f t="shared" si="4"/>
         <v>19.855466514024041</v>
       </c>
-      <c r="K38" s="10">
+      <c r="O38" s="10">
         <f t="shared" si="5"/>
         <v>11.925205113527952</v>
       </c>
-      <c r="L38" s="10">
+      <c r="P38" s="10">
         <f t="shared" si="6"/>
         <v>94.37291797965247</v>
       </c>
+      <c r="Q38" s="15"/>
+      <c r="R38" s="15"/>
+      <c r="S38" s="15"/>
     </row>
-    <row r="39" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A39" s="2">
         <f>A38+1</f>
         <v>1915</v>
@@ -5225,139 +5514,227 @@
         <v>1787310</v>
       </c>
       <c r="C39" s="2"/>
-      <c r="D39" s="4">
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="4">
         <f t="shared" si="8"/>
         <v>1687310</v>
       </c>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="3"/>
-      <c r="J39" s="3"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+      <c r="O39" s="1"/>
+      <c r="P39" s="1"/>
     </row>
-    <row r="40" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A40" s="12" t="s">
         <v>9</v>
       </c>
       <c r="B40" s="12"/>
       <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
+      <c r="D40" s="13" cm="1">
+        <f t="array" ref="D40">SUM(D5+D5:D19)</f>
+        <v>0</v>
+      </c>
+      <c r="E40" s="13" cm="1">
+        <f t="array" ref="E40">SUM(E5+E5:E19)</f>
+        <v>0</v>
+      </c>
       <c r="F40" s="13" cm="1">
         <f t="array" ref="F40">SUM(F5+F5:F19)</f>
-        <v>1510500</v>
+        <v>0</v>
       </c>
       <c r="G40" s="13" cm="1">
         <f t="array" ref="G40">SUM(G5+G5:G19)</f>
+        <v>0</v>
+      </c>
+      <c r="H40" s="12"/>
+      <c r="I40" s="12"/>
+      <c r="J40" s="13" cm="1">
+        <f t="array" ref="J40">SUM(J5+J5:J19)</f>
+        <v>1510500</v>
+      </c>
+      <c r="K40" s="13" cm="1">
+        <f t="array" ref="K40">SUM(K5+K5:K19)</f>
         <v>910500</v>
       </c>
-      <c r="H40" s="13" cm="1">
-        <f t="array" ref="H40">SUM(H5+H5:H19)</f>
+      <c r="L40" s="13" cm="1">
+        <f t="array" ref="L40">SUM(L5+L5:L19)</f>
         <v>2550</v>
       </c>
-      <c r="I40" s="11">
-        <f>AVERAGE(I5:I19)</f>
+      <c r="M40" s="11">
+        <f>AVERAGE(M5:M19)</f>
         <v>44.284960471317206</v>
       </c>
-      <c r="J40" s="11">
-        <f>AVERAGE(J5:J19)</f>
+      <c r="N40" s="11">
+        <f>AVERAGE(N5:N19)</f>
         <v>26.804245110008651</v>
       </c>
-      <c r="K40" s="11">
-        <f>AVERAGE(K5:K19)</f>
+      <c r="O40" s="11">
+        <f>AVERAGE(O5:O19)</f>
         <v>17.480715361308548</v>
       </c>
-      <c r="L40" s="11">
-        <f>AVERAGE(L5:L19)</f>
+      <c r="P40" s="11">
+        <f>AVERAGE(P5:P19)</f>
         <v>91.965609066958763</v>
       </c>
+      <c r="Q40" s="13" cm="1">
+        <f t="array" ref="Q40">SUM(Q5+Q5:Q19)</f>
+        <v>0</v>
+      </c>
+      <c r="R40" s="13" cm="1">
+        <f t="array" ref="R40">SUM(R5+R5:R19)</f>
+        <v>0</v>
+      </c>
+      <c r="S40" s="13" cm="1">
+        <f t="array" ref="S40">SUM(S5+S5:S19)</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A41" s="12" t="s">
         <v>10</v>
       </c>
       <c r="B41" s="12"/>
       <c r="C41" s="12"/>
-      <c r="D41" s="12"/>
-      <c r="E41" s="12"/>
+      <c r="D41" s="13">
+        <f>SUM(D20:D38)</f>
+        <v>0</v>
+      </c>
+      <c r="E41" s="13">
+        <f>SUM(E20:E38)</f>
+        <v>0</v>
+      </c>
       <c r="F41" s="13">
         <f>SUM(F20:F38)</f>
-        <v>995600</v>
+        <v>0</v>
       </c>
       <c r="G41" s="13">
         <f>SUM(G20:G38)</f>
+        <v>0</v>
+      </c>
+      <c r="H41" s="12"/>
+      <c r="I41" s="12"/>
+      <c r="J41" s="13">
+        <f>SUM(J20:J38)</f>
+        <v>995600</v>
+      </c>
+      <c r="K41" s="13">
+        <f>SUM(K20:K38)</f>
         <v>615600</v>
       </c>
-      <c r="H41" s="13">
-        <f>SUM(H20:H38)</f>
+      <c r="L41" s="13">
+        <f>SUM(L20:L38)</f>
         <v>5510</v>
       </c>
-      <c r="I41" s="11">
-        <f>AVERAGE(I20:I38)</f>
+      <c r="M41" s="11">
+        <f>AVERAGE(M20:M38)</f>
         <v>35.235984922749225</v>
       </c>
-      <c r="J41" s="11">
-        <f>AVERAGE(J20:J38)</f>
+      <c r="N41" s="11">
+        <f>AVERAGE(N20:N38)</f>
         <v>21.776627722165703</v>
       </c>
-      <c r="K41" s="11">
-        <f>AVERAGE(K20:K38)</f>
+      <c r="O41" s="11">
+        <f>AVERAGE(O20:O38)</f>
         <v>13.45935720058352</v>
       </c>
-      <c r="L41" s="11">
-        <f>AVERAGE(L20:L38)</f>
+      <c r="P41" s="11">
+        <f>AVERAGE(P20:P38)</f>
         <v>93.696736470681046</v>
       </c>
+      <c r="Q41" s="13">
+        <f>SUM(Q20:Q38)</f>
+        <v>0</v>
+      </c>
+      <c r="R41" s="13">
+        <f>SUM(R20:R38)</f>
+        <v>0</v>
+      </c>
+      <c r="S41" s="13">
+        <f>SUM(S20:S38)</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A42" s="12" t="s">
         <v>11</v>
       </c>
       <c r="B42" s="12"/>
       <c r="C42" s="12"/>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
+      <c r="D42" s="13">
+        <f>D40+D41</f>
+        <v>0</v>
+      </c>
+      <c r="E42" s="13">
+        <f>E40+E41</f>
+        <v>0</v>
+      </c>
       <c r="F42" s="13">
         <f>F40+F41</f>
-        <v>2506100</v>
+        <v>0</v>
       </c>
       <c r="G42" s="13">
         <f>G40+G41</f>
+        <v>0</v>
+      </c>
+      <c r="H42" s="12"/>
+      <c r="I42" s="12"/>
+      <c r="J42" s="13">
+        <f>J40+J41</f>
+        <v>2506100</v>
+      </c>
+      <c r="K42" s="13">
+        <f>K40+K41</f>
         <v>1526100</v>
       </c>
-      <c r="H42" s="13">
-        <f>H40+H41</f>
+      <c r="L42" s="13">
+        <f>L40+L41</f>
         <v>8060</v>
       </c>
-      <c r="I42" s="11">
-        <f>AVERAGE(I5:I38)</f>
+      <c r="M42" s="11">
+        <f>AVERAGE(M5:M38)</f>
         <v>39.228180017705675</v>
       </c>
-      <c r="J42" s="11">
-        <f>AVERAGE(J5:J38)</f>
+      <c r="N42" s="11">
+        <f>AVERAGE(N5:N38)</f>
         <v>23.994694216802294</v>
       </c>
-      <c r="K42" s="11">
-        <f>AVERAGE(K5:K38)</f>
+      <c r="O42" s="11">
+        <f>AVERAGE(O5:O38)</f>
         <v>15.233485800903388</v>
       </c>
-      <c r="L42" s="11">
-        <f>AVERAGE(L5:L38)</f>
+      <c r="P42" s="11">
+        <f>AVERAGE(P5:P38)</f>
         <v>92.933003792568272</v>
+      </c>
+      <c r="Q42" s="13">
+        <f>Q40+Q41</f>
+        <v>0</v>
+      </c>
+      <c r="R42" s="13">
+        <f>R40+R41</f>
+        <v>0</v>
+      </c>
+      <c r="S42" s="13">
+        <f>S40+S41</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:L3"/>
+    <mergeCell ref="H3:S3"/>
+    <mergeCell ref="B3:G3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="D6:D38" formula="1"/>
+    <ignoredError sqref="H6:H38" formula="1"/>
   </ignoredErrors>
   <drawing r:id="rId2"/>
 </worksheet>

--- a/rtss-pre1917/src/main/resources/excel-templates/composite-taxon-1881-1914.xlsx
+++ b/rtss-pre1917/src/main/resources/excel-templates/composite-taxon-1881-1914.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\excel-templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D415170-33DB-4BCF-B5F3-63E19DB95152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42D91A14-FEB7-4DDF-9C79-CFA45F697E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{BB18BFB1-C03A-41FE-BE1A-93D139757D6D}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{BB18BFB1-C03A-41FE-BE1A-93D139757D6D}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
   <si>
     <t>XXX</t>
   </si>
@@ -119,6 +119,21 @@
   <si>
     <t>внутр. мигр</t>
   </si>
+  <si>
+    <t>прирост населения</t>
+  </si>
+  <si>
+    <t>общего</t>
+  </si>
+  <si>
+    <t>ест.</t>
+  </si>
+  <si>
+    <t>ест.+мех.</t>
+  </si>
+  <si>
+    <t>verify</t>
+  </si>
 </sst>
 </file>
 
@@ -127,7 +142,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -162,8 +177,16 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -194,6 +217,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -207,7 +236,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -243,6 +272,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3435,7 +3470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12B321D7-C433-4B50-AA6E-BF1C75F28F7F}">
-  <dimension ref="A1:S42"/>
+  <dimension ref="A1:Y42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="11.26171875" customWidth="1"/>
@@ -3453,7 +3488,7 @@
     <col min="19" max="19" width="11.3671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="23.1" x14ac:dyDescent="0.85">
+    <row r="1" spans="1:25" ht="23.1" x14ac:dyDescent="0.85">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -3471,7 +3506,7 @@
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
     </row>
-    <row r="2" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3487,7 +3522,7 @@
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
     </row>
-    <row r="3" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
@@ -3513,8 +3548,13 @@
       <c r="Q3" s="16"/>
       <c r="R3" s="16"/>
       <c r="S3" s="16"/>
+      <c r="U3" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="V3" s="18"/>
+      <c r="W3" s="18"/>
     </row>
-    <row r="4" spans="1:19" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:25" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="8"/>
       <c r="B4" s="14" t="s">
         <v>2</v>
@@ -3570,8 +3610,20 @@
       <c r="S4" s="8" t="s">
         <v>18</v>
       </c>
+      <c r="U4" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="V4" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="W4" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y4" s="8" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="5" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A5" s="2">
         <v>1881</v>
       </c>
@@ -3622,8 +3674,24 @@
       <c r="Q5" s="15"/>
       <c r="R5" s="15"/>
       <c r="S5" s="15"/>
+      <c r="U5" s="15">
+        <f>B6-B5</f>
+        <v>20050</v>
+      </c>
+      <c r="V5" s="15">
+        <f>J5-K5</f>
+        <v>20000</v>
+      </c>
+      <c r="W5" s="15">
+        <f>V5+L5</f>
+        <v>20050</v>
+      </c>
+      <c r="Y5" s="15">
+        <f>H6-H5-W5</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A6" s="2">
         <f>A5+1</f>
         <v>1882</v>
@@ -3679,10 +3747,26 @@
       <c r="Q6" s="15"/>
       <c r="R6" s="15"/>
       <c r="S6" s="15"/>
+      <c r="U6" s="15">
+        <f t="shared" ref="U6:U38" si="7">B7-B6</f>
+        <v>20060</v>
+      </c>
+      <c r="V6" s="15">
+        <f t="shared" ref="V6:V38" si="8">J6-K6</f>
+        <v>20000</v>
+      </c>
+      <c r="W6" s="15">
+        <f t="shared" ref="W6:W38" si="9">V6+L6</f>
+        <v>20060</v>
+      </c>
+      <c r="Y6" s="15">
+        <f t="shared" ref="Y6:Y38" si="10">H7-H6-W6</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A7" s="2">
-        <f t="shared" ref="A7:A37" si="7">A6+1</f>
+        <f t="shared" ref="A7:A37" si="11">A6+1</f>
         <v>1883</v>
       </c>
       <c r="B7" s="4">
@@ -3698,7 +3782,7 @@
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
       <c r="H7" s="4">
-        <f t="shared" ref="H7:H39" si="8">H6+J6-K6+L6</f>
+        <f t="shared" ref="H7:H39" si="12">H6+J6-K6+L6</f>
         <v>1040110</v>
       </c>
       <c r="I7" s="4">
@@ -3706,15 +3790,15 @@
         <v>1050145</v>
       </c>
       <c r="J7" s="4">
-        <f t="shared" ref="J7:J38" si="9">J6+100</f>
+        <f t="shared" ref="J7:J38" si="13">J6+100</f>
         <v>50200</v>
       </c>
       <c r="K7" s="4">
-        <f t="shared" ref="K7:K38" si="10">K6+100</f>
+        <f t="shared" ref="K7:K38" si="14">K6+100</f>
         <v>30200</v>
       </c>
       <c r="L7" s="4">
-        <f t="shared" ref="L7:L38" si="11">L6+10</f>
+        <f t="shared" ref="L7:L38" si="15">L6+10</f>
         <v>70</v>
       </c>
       <c r="M7" s="5">
@@ -3736,10 +3820,26 @@
       <c r="Q7" s="15"/>
       <c r="R7" s="15"/>
       <c r="S7" s="15"/>
+      <c r="U7" s="15">
+        <f t="shared" si="7"/>
+        <v>20070</v>
+      </c>
+      <c r="V7" s="15">
+        <f t="shared" si="8"/>
+        <v>20000</v>
+      </c>
+      <c r="W7" s="15">
+        <f t="shared" si="9"/>
+        <v>20070</v>
+      </c>
+      <c r="Y7" s="15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A8" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1884</v>
       </c>
       <c r="B8" s="4">
@@ -3755,7 +3855,7 @@
       <c r="F8" s="9"/>
       <c r="G8" s="9"/>
       <c r="H8" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1060180</v>
       </c>
       <c r="I8" s="4">
@@ -3763,15 +3863,15 @@
         <v>1070220</v>
       </c>
       <c r="J8" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>50300</v>
       </c>
       <c r="K8" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>30300</v>
       </c>
       <c r="L8" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>80</v>
       </c>
       <c r="M8" s="5">
@@ -3793,10 +3893,26 @@
       <c r="Q8" s="15"/>
       <c r="R8" s="15"/>
       <c r="S8" s="15"/>
+      <c r="U8" s="15">
+        <f t="shared" si="7"/>
+        <v>20080</v>
+      </c>
+      <c r="V8" s="15">
+        <f t="shared" si="8"/>
+        <v>20000</v>
+      </c>
+      <c r="W8" s="15">
+        <f t="shared" si="9"/>
+        <v>20080</v>
+      </c>
+      <c r="Y8" s="15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A9" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1885</v>
       </c>
       <c r="B9" s="4">
@@ -3812,7 +3928,7 @@
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
       <c r="H9" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1080260</v>
       </c>
       <c r="I9" s="4">
@@ -3820,15 +3936,15 @@
         <v>1090305</v>
       </c>
       <c r="J9" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>50400</v>
       </c>
       <c r="K9" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>30400</v>
       </c>
       <c r="L9" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>90</v>
       </c>
       <c r="M9" s="5">
@@ -3850,10 +3966,26 @@
       <c r="Q9" s="15"/>
       <c r="R9" s="15"/>
       <c r="S9" s="15"/>
+      <c r="U9" s="15">
+        <f t="shared" si="7"/>
+        <v>20090</v>
+      </c>
+      <c r="V9" s="15">
+        <f t="shared" si="8"/>
+        <v>20000</v>
+      </c>
+      <c r="W9" s="15">
+        <f t="shared" si="9"/>
+        <v>20090</v>
+      </c>
+      <c r="Y9" s="15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A10" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1886</v>
       </c>
       <c r="B10" s="4">
@@ -3869,7 +4001,7 @@
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
       <c r="H10" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1100350</v>
       </c>
       <c r="I10" s="4">
@@ -3877,15 +4009,15 @@
         <v>1110400</v>
       </c>
       <c r="J10" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>50500</v>
       </c>
       <c r="K10" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>30500</v>
       </c>
       <c r="L10" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>100</v>
       </c>
       <c r="M10" s="5">
@@ -3907,10 +4039,26 @@
       <c r="Q10" s="15"/>
       <c r="R10" s="15"/>
       <c r="S10" s="15"/>
+      <c r="U10" s="15">
+        <f t="shared" si="7"/>
+        <v>20100</v>
+      </c>
+      <c r="V10" s="15">
+        <f t="shared" si="8"/>
+        <v>20000</v>
+      </c>
+      <c r="W10" s="15">
+        <f t="shared" si="9"/>
+        <v>20100</v>
+      </c>
+      <c r="Y10" s="15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A11" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1887</v>
       </c>
       <c r="B11" s="4">
@@ -3926,7 +4074,7 @@
       <c r="F11" s="9"/>
       <c r="G11" s="9"/>
       <c r="H11" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1120450</v>
       </c>
       <c r="I11" s="4">
@@ -3934,15 +4082,15 @@
         <v>1130505</v>
       </c>
       <c r="J11" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>50600</v>
       </c>
       <c r="K11" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>30600</v>
       </c>
       <c r="L11" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>110</v>
       </c>
       <c r="M11" s="5">
@@ -3964,10 +4112,26 @@
       <c r="Q11" s="15"/>
       <c r="R11" s="15"/>
       <c r="S11" s="15"/>
+      <c r="U11" s="15">
+        <f t="shared" si="7"/>
+        <v>20110</v>
+      </c>
+      <c r="V11" s="15">
+        <f t="shared" si="8"/>
+        <v>20000</v>
+      </c>
+      <c r="W11" s="15">
+        <f t="shared" si="9"/>
+        <v>20110</v>
+      </c>
+      <c r="Y11" s="15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A12" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1888</v>
       </c>
       <c r="B12" s="4">
@@ -3983,7 +4147,7 @@
       <c r="F12" s="9"/>
       <c r="G12" s="9"/>
       <c r="H12" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1140560</v>
       </c>
       <c r="I12" s="4">
@@ -3991,15 +4155,15 @@
         <v>1150620</v>
       </c>
       <c r="J12" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>50700</v>
       </c>
       <c r="K12" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>30700</v>
       </c>
       <c r="L12" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>120</v>
       </c>
       <c r="M12" s="5">
@@ -4021,10 +4185,26 @@
       <c r="Q12" s="15"/>
       <c r="R12" s="15"/>
       <c r="S12" s="15"/>
+      <c r="U12" s="15">
+        <f t="shared" si="7"/>
+        <v>20120</v>
+      </c>
+      <c r="V12" s="15">
+        <f t="shared" si="8"/>
+        <v>20000</v>
+      </c>
+      <c r="W12" s="15">
+        <f t="shared" si="9"/>
+        <v>20120</v>
+      </c>
+      <c r="Y12" s="15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A13" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1889</v>
       </c>
       <c r="B13" s="4">
@@ -4040,7 +4220,7 @@
       <c r="F13" s="9"/>
       <c r="G13" s="9"/>
       <c r="H13" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1160680</v>
       </c>
       <c r="I13" s="4">
@@ -4048,15 +4228,15 @@
         <v>1170745</v>
       </c>
       <c r="J13" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>50800</v>
       </c>
       <c r="K13" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>30800</v>
       </c>
       <c r="L13" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>130</v>
       </c>
       <c r="M13" s="5">
@@ -4078,10 +4258,26 @@
       <c r="Q13" s="15"/>
       <c r="R13" s="15"/>
       <c r="S13" s="15"/>
+      <c r="U13" s="15">
+        <f t="shared" si="7"/>
+        <v>20130</v>
+      </c>
+      <c r="V13" s="15">
+        <f t="shared" si="8"/>
+        <v>20000</v>
+      </c>
+      <c r="W13" s="15">
+        <f t="shared" si="9"/>
+        <v>20130</v>
+      </c>
+      <c r="Y13" s="15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A14" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1890</v>
       </c>
       <c r="B14" s="4">
@@ -4097,7 +4293,7 @@
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
       <c r="H14" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1180810</v>
       </c>
       <c r="I14" s="4">
@@ -4105,15 +4301,15 @@
         <v>1190880</v>
       </c>
       <c r="J14" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>50900</v>
       </c>
       <c r="K14" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>30900</v>
       </c>
       <c r="L14" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>140</v>
       </c>
       <c r="M14" s="5">
@@ -4135,10 +4331,26 @@
       <c r="Q14" s="15"/>
       <c r="R14" s="15"/>
       <c r="S14" s="15"/>
+      <c r="U14" s="15">
+        <f t="shared" si="7"/>
+        <v>20140</v>
+      </c>
+      <c r="V14" s="15">
+        <f t="shared" si="8"/>
+        <v>20000</v>
+      </c>
+      <c r="W14" s="15">
+        <f t="shared" si="9"/>
+        <v>20140</v>
+      </c>
+      <c r="Y14" s="15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A15" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1891</v>
       </c>
       <c r="B15" s="4">
@@ -4154,7 +4366,7 @@
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
       <c r="H15" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1200950</v>
       </c>
       <c r="I15" s="4">
@@ -4162,15 +4374,15 @@
         <v>1211025</v>
       </c>
       <c r="J15" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>51000</v>
       </c>
       <c r="K15" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>31000</v>
       </c>
       <c r="L15" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>150</v>
       </c>
       <c r="M15" s="5">
@@ -4192,10 +4404,26 @@
       <c r="Q15" s="15"/>
       <c r="R15" s="15"/>
       <c r="S15" s="15"/>
+      <c r="U15" s="15">
+        <f t="shared" si="7"/>
+        <v>20150</v>
+      </c>
+      <c r="V15" s="15">
+        <f t="shared" si="8"/>
+        <v>20000</v>
+      </c>
+      <c r="W15" s="15">
+        <f t="shared" si="9"/>
+        <v>20150</v>
+      </c>
+      <c r="Y15" s="15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A16" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1892</v>
       </c>
       <c r="B16" s="4">
@@ -4211,7 +4439,7 @@
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
       <c r="H16" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1221100</v>
       </c>
       <c r="I16" s="4">
@@ -4219,15 +4447,15 @@
         <v>1231180</v>
       </c>
       <c r="J16" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>51100</v>
       </c>
       <c r="K16" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>31100</v>
       </c>
       <c r="L16" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>160</v>
       </c>
       <c r="M16" s="5">
@@ -4249,10 +4477,26 @@
       <c r="Q16" s="15"/>
       <c r="R16" s="15"/>
       <c r="S16" s="15"/>
+      <c r="U16" s="15">
+        <f t="shared" si="7"/>
+        <v>20160</v>
+      </c>
+      <c r="V16" s="15">
+        <f t="shared" si="8"/>
+        <v>20000</v>
+      </c>
+      <c r="W16" s="15">
+        <f t="shared" si="9"/>
+        <v>20160</v>
+      </c>
+      <c r="Y16" s="15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A17" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1893</v>
       </c>
       <c r="B17" s="4">
@@ -4268,7 +4512,7 @@
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
       <c r="H17" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1241260</v>
       </c>
       <c r="I17" s="4">
@@ -4276,15 +4520,15 @@
         <v>1251345</v>
       </c>
       <c r="J17" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>51200</v>
       </c>
       <c r="K17" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>31200</v>
       </c>
       <c r="L17" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>170</v>
       </c>
       <c r="M17" s="5">
@@ -4306,10 +4550,26 @@
       <c r="Q17" s="15"/>
       <c r="R17" s="15"/>
       <c r="S17" s="15"/>
+      <c r="U17" s="15">
+        <f t="shared" si="7"/>
+        <v>20170</v>
+      </c>
+      <c r="V17" s="15">
+        <f t="shared" si="8"/>
+        <v>20000</v>
+      </c>
+      <c r="W17" s="15">
+        <f t="shared" si="9"/>
+        <v>20170</v>
+      </c>
+      <c r="Y17" s="15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A18" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1894</v>
       </c>
       <c r="B18" s="4">
@@ -4325,7 +4585,7 @@
       <c r="F18" s="9"/>
       <c r="G18" s="9"/>
       <c r="H18" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1261430</v>
       </c>
       <c r="I18" s="4">
@@ -4333,15 +4593,15 @@
         <v>1271520</v>
       </c>
       <c r="J18" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>51300</v>
       </c>
       <c r="K18" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>31300</v>
       </c>
       <c r="L18" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>180</v>
       </c>
       <c r="M18" s="5">
@@ -4363,10 +4623,26 @@
       <c r="Q18" s="15"/>
       <c r="R18" s="15"/>
       <c r="S18" s="15"/>
+      <c r="U18" s="15">
+        <f t="shared" si="7"/>
+        <v>20180</v>
+      </c>
+      <c r="V18" s="15">
+        <f t="shared" si="8"/>
+        <v>20000</v>
+      </c>
+      <c r="W18" s="15">
+        <f t="shared" si="9"/>
+        <v>20180</v>
+      </c>
+      <c r="Y18" s="15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="19" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A19" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1895</v>
       </c>
       <c r="B19" s="4">
@@ -4382,7 +4658,7 @@
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
       <c r="H19" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1281610</v>
       </c>
       <c r="I19" s="4">
@@ -4390,15 +4666,15 @@
         <v>1291705</v>
       </c>
       <c r="J19" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>51400</v>
       </c>
       <c r="K19" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>31400</v>
       </c>
       <c r="L19" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>190</v>
       </c>
       <c r="M19" s="5">
@@ -4420,10 +4696,26 @@
       <c r="Q19" s="15"/>
       <c r="R19" s="15"/>
       <c r="S19" s="15"/>
+      <c r="U19" s="15">
+        <f t="shared" si="7"/>
+        <v>20190</v>
+      </c>
+      <c r="V19" s="15">
+        <f t="shared" si="8"/>
+        <v>20000</v>
+      </c>
+      <c r="W19" s="15">
+        <f t="shared" si="9"/>
+        <v>20190</v>
+      </c>
+      <c r="Y19" s="15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="20" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A20" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1896</v>
       </c>
       <c r="B20" s="4">
@@ -4439,7 +4731,7 @@
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
       <c r="H20" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1301800</v>
       </c>
       <c r="I20" s="4">
@@ -4447,15 +4739,15 @@
         <v>1311900</v>
       </c>
       <c r="J20" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>51500</v>
       </c>
       <c r="K20" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>31500</v>
       </c>
       <c r="L20" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>200</v>
       </c>
       <c r="M20" s="5">
@@ -4477,10 +4769,26 @@
       <c r="Q20" s="15"/>
       <c r="R20" s="15"/>
       <c r="S20" s="15"/>
+      <c r="U20" s="15">
+        <f t="shared" si="7"/>
+        <v>20200</v>
+      </c>
+      <c r="V20" s="15">
+        <f t="shared" si="8"/>
+        <v>20000</v>
+      </c>
+      <c r="W20" s="15">
+        <f t="shared" si="9"/>
+        <v>20200</v>
+      </c>
+      <c r="Y20" s="15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A21" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1897</v>
       </c>
       <c r="B21" s="4">
@@ -4496,7 +4804,7 @@
       <c r="F21" s="9"/>
       <c r="G21" s="9"/>
       <c r="H21" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1322000</v>
       </c>
       <c r="I21" s="4">
@@ -4504,15 +4812,15 @@
         <v>1332105</v>
       </c>
       <c r="J21" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>51600</v>
       </c>
       <c r="K21" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>31600</v>
       </c>
       <c r="L21" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>210</v>
       </c>
       <c r="M21" s="5">
@@ -4534,10 +4842,26 @@
       <c r="Q21" s="15"/>
       <c r="R21" s="15"/>
       <c r="S21" s="15"/>
+      <c r="U21" s="15">
+        <f t="shared" si="7"/>
+        <v>20210</v>
+      </c>
+      <c r="V21" s="15">
+        <f t="shared" si="8"/>
+        <v>20000</v>
+      </c>
+      <c r="W21" s="15">
+        <f t="shared" si="9"/>
+        <v>20210</v>
+      </c>
+      <c r="Y21" s="15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="22" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="22" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A22" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1898</v>
       </c>
       <c r="B22" s="4">
@@ -4553,7 +4877,7 @@
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
       <c r="H22" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1342210</v>
       </c>
       <c r="I22" s="4">
@@ -4561,15 +4885,15 @@
         <v>1352320</v>
       </c>
       <c r="J22" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>51700</v>
       </c>
       <c r="K22" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>31700</v>
       </c>
       <c r="L22" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>220</v>
       </c>
       <c r="M22" s="5">
@@ -4591,10 +4915,26 @@
       <c r="Q22" s="15"/>
       <c r="R22" s="15"/>
       <c r="S22" s="15"/>
+      <c r="U22" s="15">
+        <f t="shared" si="7"/>
+        <v>20220</v>
+      </c>
+      <c r="V22" s="15">
+        <f t="shared" si="8"/>
+        <v>20000</v>
+      </c>
+      <c r="W22" s="15">
+        <f t="shared" si="9"/>
+        <v>20220</v>
+      </c>
+      <c r="Y22" s="15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="23" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A23" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1899</v>
       </c>
       <c r="B23" s="4">
@@ -4610,7 +4950,7 @@
       <c r="F23" s="9"/>
       <c r="G23" s="9"/>
       <c r="H23" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1362430</v>
       </c>
       <c r="I23" s="4">
@@ -4618,15 +4958,15 @@
         <v>1372545</v>
       </c>
       <c r="J23" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>51800</v>
       </c>
       <c r="K23" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>31800</v>
       </c>
       <c r="L23" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>230</v>
       </c>
       <c r="M23" s="5">
@@ -4648,10 +4988,26 @@
       <c r="Q23" s="15"/>
       <c r="R23" s="15"/>
       <c r="S23" s="15"/>
+      <c r="U23" s="15">
+        <f t="shared" si="7"/>
+        <v>20230</v>
+      </c>
+      <c r="V23" s="15">
+        <f t="shared" si="8"/>
+        <v>20000</v>
+      </c>
+      <c r="W23" s="15">
+        <f t="shared" si="9"/>
+        <v>20230</v>
+      </c>
+      <c r="Y23" s="15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="24" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A24" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1900</v>
       </c>
       <c r="B24" s="4">
@@ -4667,7 +5023,7 @@
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
       <c r="H24" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1382660</v>
       </c>
       <c r="I24" s="4">
@@ -4675,15 +5031,15 @@
         <v>1392780</v>
       </c>
       <c r="J24" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>51900</v>
       </c>
       <c r="K24" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>31900</v>
       </c>
       <c r="L24" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>240</v>
       </c>
       <c r="M24" s="5">
@@ -4705,10 +5061,26 @@
       <c r="Q24" s="15"/>
       <c r="R24" s="15"/>
       <c r="S24" s="15"/>
+      <c r="U24" s="15">
+        <f t="shared" si="7"/>
+        <v>20240</v>
+      </c>
+      <c r="V24" s="15">
+        <f t="shared" si="8"/>
+        <v>20000</v>
+      </c>
+      <c r="W24" s="15">
+        <f t="shared" si="9"/>
+        <v>20240</v>
+      </c>
+      <c r="Y24" s="15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="25" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A25" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1901</v>
       </c>
       <c r="B25" s="4">
@@ -4724,7 +5096,7 @@
       <c r="F25" s="9"/>
       <c r="G25" s="9"/>
       <c r="H25" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1402900</v>
       </c>
       <c r="I25" s="4">
@@ -4732,15 +5104,15 @@
         <v>1413025</v>
       </c>
       <c r="J25" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>52000</v>
       </c>
       <c r="K25" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>32000</v>
       </c>
       <c r="L25" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>250</v>
       </c>
       <c r="M25" s="5">
@@ -4762,10 +5134,26 @@
       <c r="Q25" s="15"/>
       <c r="R25" s="15"/>
       <c r="S25" s="15"/>
+      <c r="U25" s="15">
+        <f t="shared" si="7"/>
+        <v>20250</v>
+      </c>
+      <c r="V25" s="15">
+        <f t="shared" si="8"/>
+        <v>20000</v>
+      </c>
+      <c r="W25" s="15">
+        <f t="shared" si="9"/>
+        <v>20250</v>
+      </c>
+      <c r="Y25" s="15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="26" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A26" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1902</v>
       </c>
       <c r="B26" s="4">
@@ -4781,7 +5169,7 @@
       <c r="F26" s="9"/>
       <c r="G26" s="9"/>
       <c r="H26" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1423150</v>
       </c>
       <c r="I26" s="4">
@@ -4789,15 +5177,15 @@
         <v>1433280</v>
       </c>
       <c r="J26" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>52100</v>
       </c>
       <c r="K26" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>32100</v>
       </c>
       <c r="L26" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>260</v>
       </c>
       <c r="M26" s="5">
@@ -4819,10 +5207,26 @@
       <c r="Q26" s="15"/>
       <c r="R26" s="15"/>
       <c r="S26" s="15"/>
+      <c r="U26" s="15">
+        <f t="shared" si="7"/>
+        <v>20260</v>
+      </c>
+      <c r="V26" s="15">
+        <f t="shared" si="8"/>
+        <v>20000</v>
+      </c>
+      <c r="W26" s="15">
+        <f t="shared" si="9"/>
+        <v>20260</v>
+      </c>
+      <c r="Y26" s="15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="27" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="27" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A27" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1903</v>
       </c>
       <c r="B27" s="4">
@@ -4838,7 +5242,7 @@
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
       <c r="H27" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1443410</v>
       </c>
       <c r="I27" s="4">
@@ -4846,15 +5250,15 @@
         <v>1453545</v>
       </c>
       <c r="J27" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>52200</v>
       </c>
       <c r="K27" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>32200</v>
       </c>
       <c r="L27" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>270</v>
       </c>
       <c r="M27" s="5">
@@ -4876,10 +5280,26 @@
       <c r="Q27" s="15"/>
       <c r="R27" s="15"/>
       <c r="S27" s="15"/>
+      <c r="U27" s="15">
+        <f t="shared" si="7"/>
+        <v>20270</v>
+      </c>
+      <c r="V27" s="15">
+        <f t="shared" si="8"/>
+        <v>20000</v>
+      </c>
+      <c r="W27" s="15">
+        <f t="shared" si="9"/>
+        <v>20270</v>
+      </c>
+      <c r="Y27" s="15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="28" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A28" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1904</v>
       </c>
       <c r="B28" s="4">
@@ -4895,7 +5315,7 @@
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
       <c r="H28" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1463680</v>
       </c>
       <c r="I28" s="4">
@@ -4903,15 +5323,15 @@
         <v>1473820</v>
       </c>
       <c r="J28" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>52300</v>
       </c>
       <c r="K28" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>32300</v>
       </c>
       <c r="L28" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>280</v>
       </c>
       <c r="M28" s="5">
@@ -4933,10 +5353,26 @@
       <c r="Q28" s="15"/>
       <c r="R28" s="15"/>
       <c r="S28" s="15"/>
+      <c r="U28" s="15">
+        <f t="shared" si="7"/>
+        <v>20280</v>
+      </c>
+      <c r="V28" s="15">
+        <f t="shared" si="8"/>
+        <v>20000</v>
+      </c>
+      <c r="W28" s="15">
+        <f t="shared" si="9"/>
+        <v>20280</v>
+      </c>
+      <c r="Y28" s="15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="29" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A29" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1905</v>
       </c>
       <c r="B29" s="4">
@@ -4952,7 +5388,7 @@
       <c r="F29" s="9"/>
       <c r="G29" s="9"/>
       <c r="H29" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1483960</v>
       </c>
       <c r="I29" s="4">
@@ -4960,15 +5396,15 @@
         <v>1494105</v>
       </c>
       <c r="J29" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>52400</v>
       </c>
       <c r="K29" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>32400</v>
       </c>
       <c r="L29" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>290</v>
       </c>
       <c r="M29" s="5">
@@ -4990,10 +5426,26 @@
       <c r="Q29" s="15"/>
       <c r="R29" s="15"/>
       <c r="S29" s="15"/>
+      <c r="U29" s="15">
+        <f t="shared" si="7"/>
+        <v>20290</v>
+      </c>
+      <c r="V29" s="15">
+        <f t="shared" si="8"/>
+        <v>20000</v>
+      </c>
+      <c r="W29" s="15">
+        <f t="shared" si="9"/>
+        <v>20290</v>
+      </c>
+      <c r="Y29" s="15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="30" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A30" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1906</v>
       </c>
       <c r="B30" s="4">
@@ -5009,7 +5461,7 @@
       <c r="F30" s="9"/>
       <c r="G30" s="9"/>
       <c r="H30" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1504250</v>
       </c>
       <c r="I30" s="4">
@@ -5017,15 +5469,15 @@
         <v>1514400</v>
       </c>
       <c r="J30" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>52500</v>
       </c>
       <c r="K30" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>32500</v>
       </c>
       <c r="L30" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>300</v>
       </c>
       <c r="M30" s="5">
@@ -5047,10 +5499,26 @@
       <c r="Q30" s="15"/>
       <c r="R30" s="15"/>
       <c r="S30" s="15"/>
+      <c r="U30" s="15">
+        <f t="shared" si="7"/>
+        <v>20300</v>
+      </c>
+      <c r="V30" s="15">
+        <f t="shared" si="8"/>
+        <v>20000</v>
+      </c>
+      <c r="W30" s="15">
+        <f t="shared" si="9"/>
+        <v>20300</v>
+      </c>
+      <c r="Y30" s="15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="31" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A31" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1907</v>
       </c>
       <c r="B31" s="4">
@@ -5066,7 +5534,7 @@
       <c r="F31" s="9"/>
       <c r="G31" s="9"/>
       <c r="H31" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1524550</v>
       </c>
       <c r="I31" s="4">
@@ -5074,15 +5542,15 @@
         <v>1534705</v>
       </c>
       <c r="J31" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>52600</v>
       </c>
       <c r="K31" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>32600</v>
       </c>
       <c r="L31" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>310</v>
       </c>
       <c r="M31" s="5">
@@ -5104,10 +5572,26 @@
       <c r="Q31" s="15"/>
       <c r="R31" s="15"/>
       <c r="S31" s="15"/>
+      <c r="U31" s="15">
+        <f t="shared" si="7"/>
+        <v>20310</v>
+      </c>
+      <c r="V31" s="15">
+        <f t="shared" si="8"/>
+        <v>20000</v>
+      </c>
+      <c r="W31" s="15">
+        <f t="shared" si="9"/>
+        <v>20310</v>
+      </c>
+      <c r="Y31" s="15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="32" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A32" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1908</v>
       </c>
       <c r="B32" s="4">
@@ -5123,7 +5607,7 @@
       <c r="F32" s="9"/>
       <c r="G32" s="9"/>
       <c r="H32" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1544860</v>
       </c>
       <c r="I32" s="4">
@@ -5131,15 +5615,15 @@
         <v>1555020</v>
       </c>
       <c r="J32" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>52700</v>
       </c>
       <c r="K32" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>32700</v>
       </c>
       <c r="L32" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>320</v>
       </c>
       <c r="M32" s="5">
@@ -5161,10 +5645,26 @@
       <c r="Q32" s="15"/>
       <c r="R32" s="15"/>
       <c r="S32" s="15"/>
+      <c r="U32" s="15">
+        <f t="shared" si="7"/>
+        <v>20320</v>
+      </c>
+      <c r="V32" s="15">
+        <f t="shared" si="8"/>
+        <v>20000</v>
+      </c>
+      <c r="W32" s="15">
+        <f t="shared" si="9"/>
+        <v>20320</v>
+      </c>
+      <c r="Y32" s="15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="33" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A33" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1909</v>
       </c>
       <c r="B33" s="4">
@@ -5180,7 +5680,7 @@
       <c r="F33" s="9"/>
       <c r="G33" s="9"/>
       <c r="H33" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1565180</v>
       </c>
       <c r="I33" s="4">
@@ -5188,15 +5688,15 @@
         <v>1575345</v>
       </c>
       <c r="J33" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>52800</v>
       </c>
       <c r="K33" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>32800</v>
       </c>
       <c r="L33" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>330</v>
       </c>
       <c r="M33" s="5">
@@ -5218,10 +5718,26 @@
       <c r="Q33" s="15"/>
       <c r="R33" s="15"/>
       <c r="S33" s="15"/>
+      <c r="U33" s="15">
+        <f t="shared" si="7"/>
+        <v>20330</v>
+      </c>
+      <c r="V33" s="15">
+        <f t="shared" si="8"/>
+        <v>20000</v>
+      </c>
+      <c r="W33" s="15">
+        <f t="shared" si="9"/>
+        <v>20330</v>
+      </c>
+      <c r="Y33" s="15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="34" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A34" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1910</v>
       </c>
       <c r="B34" s="4">
@@ -5237,7 +5753,7 @@
       <c r="F34" s="9"/>
       <c r="G34" s="9"/>
       <c r="H34" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1585510</v>
       </c>
       <c r="I34" s="4">
@@ -5245,15 +5761,15 @@
         <v>1595680</v>
       </c>
       <c r="J34" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>52900</v>
       </c>
       <c r="K34" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>32900</v>
       </c>
       <c r="L34" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>340</v>
       </c>
       <c r="M34" s="5">
@@ -5275,10 +5791,26 @@
       <c r="Q34" s="15"/>
       <c r="R34" s="15"/>
       <c r="S34" s="15"/>
+      <c r="U34" s="15">
+        <f t="shared" si="7"/>
+        <v>20340</v>
+      </c>
+      <c r="V34" s="15">
+        <f t="shared" si="8"/>
+        <v>20000</v>
+      </c>
+      <c r="W34" s="15">
+        <f t="shared" si="9"/>
+        <v>20340</v>
+      </c>
+      <c r="Y34" s="15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="35" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A35" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1911</v>
       </c>
       <c r="B35" s="4">
@@ -5294,7 +5826,7 @@
       <c r="F35" s="9"/>
       <c r="G35" s="9"/>
       <c r="H35" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1605850</v>
       </c>
       <c r="I35" s="4">
@@ -5302,15 +5834,15 @@
         <v>1616025</v>
       </c>
       <c r="J35" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>53000</v>
       </c>
       <c r="K35" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>33000</v>
       </c>
       <c r="L35" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>350</v>
       </c>
       <c r="M35" s="5">
@@ -5332,10 +5864,26 @@
       <c r="Q35" s="15"/>
       <c r="R35" s="15"/>
       <c r="S35" s="15"/>
+      <c r="U35" s="15">
+        <f t="shared" si="7"/>
+        <v>20350</v>
+      </c>
+      <c r="V35" s="15">
+        <f t="shared" si="8"/>
+        <v>20000</v>
+      </c>
+      <c r="W35" s="15">
+        <f t="shared" si="9"/>
+        <v>20350</v>
+      </c>
+      <c r="Y35" s="15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="36" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="36" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A36" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1912</v>
       </c>
       <c r="B36" s="4">
@@ -5351,7 +5899,7 @@
       <c r="F36" s="9"/>
       <c r="G36" s="9"/>
       <c r="H36" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1626200</v>
       </c>
       <c r="I36" s="4">
@@ -5359,15 +5907,15 @@
         <v>1636380</v>
       </c>
       <c r="J36" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>53100</v>
       </c>
       <c r="K36" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>33100</v>
       </c>
       <c r="L36" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>360</v>
       </c>
       <c r="M36" s="5">
@@ -5389,10 +5937,26 @@
       <c r="Q36" s="15"/>
       <c r="R36" s="15"/>
       <c r="S36" s="15"/>
+      <c r="U36" s="15">
+        <f t="shared" si="7"/>
+        <v>20360</v>
+      </c>
+      <c r="V36" s="15">
+        <f t="shared" si="8"/>
+        <v>20000</v>
+      </c>
+      <c r="W36" s="15">
+        <f t="shared" si="9"/>
+        <v>20360</v>
+      </c>
+      <c r="Y36" s="15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="37" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="37" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A37" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1913</v>
       </c>
       <c r="B37" s="4">
@@ -5408,7 +5972,7 @@
       <c r="F37" s="9"/>
       <c r="G37" s="9"/>
       <c r="H37" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1646560</v>
       </c>
       <c r="I37" s="4">
@@ -5416,15 +5980,15 @@
         <v>1656745</v>
       </c>
       <c r="J37" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>53200</v>
       </c>
       <c r="K37" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>33200</v>
       </c>
       <c r="L37" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>370</v>
       </c>
       <c r="M37" s="5">
@@ -5446,8 +6010,24 @@
       <c r="Q37" s="15"/>
       <c r="R37" s="15"/>
       <c r="S37" s="15"/>
+      <c r="U37" s="15">
+        <f t="shared" si="7"/>
+        <v>20370</v>
+      </c>
+      <c r="V37" s="15">
+        <f t="shared" si="8"/>
+        <v>20000</v>
+      </c>
+      <c r="W37" s="15">
+        <f t="shared" si="9"/>
+        <v>20370</v>
+      </c>
+      <c r="Y37" s="15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="38" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="38" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A38" s="2">
         <f>A37+1</f>
         <v>1914</v>
@@ -5465,7 +6045,7 @@
       <c r="F38" s="9"/>
       <c r="G38" s="9"/>
       <c r="H38" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1666930</v>
       </c>
       <c r="I38" s="4">
@@ -5473,15 +6053,15 @@
         <v>1677120</v>
       </c>
       <c r="J38" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>53300</v>
       </c>
       <c r="K38" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>33300</v>
       </c>
       <c r="L38" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>380</v>
       </c>
       <c r="M38" s="5">
@@ -5503,8 +6083,24 @@
       <c r="Q38" s="15"/>
       <c r="R38" s="15"/>
       <c r="S38" s="15"/>
+      <c r="U38" s="15">
+        <f t="shared" si="7"/>
+        <v>20380</v>
+      </c>
+      <c r="V38" s="15">
+        <f t="shared" si="8"/>
+        <v>20000</v>
+      </c>
+      <c r="W38" s="15">
+        <f t="shared" si="9"/>
+        <v>20380</v>
+      </c>
+      <c r="Y38" s="15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="39" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="39" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A39" s="2">
         <f>A38+1</f>
         <v>1915</v>
@@ -5519,7 +6115,7 @@
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
       <c r="H39" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1687310</v>
       </c>
       <c r="I39" s="4"/>
@@ -5531,7 +6127,7 @@
       <c r="O39" s="1"/>
       <c r="P39" s="1"/>
     </row>
-    <row r="40" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="40" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A40" s="12" t="s">
         <v>9</v>
       </c>
@@ -5595,8 +6191,20 @@
         <f t="array" ref="S40">SUM(S5+S5:S19)</f>
         <v>0</v>
       </c>
+      <c r="U40" s="13" cm="1">
+        <f t="array" ref="U40">SUM(U5+U5:U19)</f>
+        <v>602550</v>
+      </c>
+      <c r="V40" s="13" cm="1">
+        <f t="array" ref="V40">SUM(V5+V5:V19)</f>
+        <v>600000</v>
+      </c>
+      <c r="W40" s="13" cm="1">
+        <f t="array" ref="W40">SUM(W5+W5:W19)</f>
+        <v>602550</v>
+      </c>
     </row>
-    <row r="41" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="41" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A41" s="12" t="s">
         <v>10</v>
       </c>
@@ -5660,8 +6268,20 @@
         <f>SUM(S20:S38)</f>
         <v>0</v>
       </c>
+      <c r="U41" s="13">
+        <f>SUM(U20:U38)</f>
+        <v>385510</v>
+      </c>
+      <c r="V41" s="13">
+        <f>SUM(V20:V38)</f>
+        <v>380000</v>
+      </c>
+      <c r="W41" s="13">
+        <f>SUM(W20:W38)</f>
+        <v>385510</v>
+      </c>
     </row>
-    <row r="42" spans="1:19" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="42" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A42" s="12" t="s">
         <v>11</v>
       </c>
@@ -5725,11 +6345,24 @@
         <f>S40+S41</f>
         <v>0</v>
       </c>
+      <c r="U42" s="13">
+        <f>U40+U41</f>
+        <v>988060</v>
+      </c>
+      <c r="V42" s="13">
+        <f>V40+V41</f>
+        <v>980000</v>
+      </c>
+      <c r="W42" s="13">
+        <f>W40+W41</f>
+        <v>988060</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="H3:S3"/>
     <mergeCell ref="B3:G3"/>
+    <mergeCell ref="U3:W3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/rtss-pre1917/src/main/resources/excel-templates/composite-taxon-1881-1914.xlsx
+++ b/rtss-pre1917/src/main/resources/excel-templates/composite-taxon-1881-1914.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\excel-templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42D91A14-FEB7-4DDF-9C79-CFA45F697E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA2BB114-D24D-4817-8620-4171CEE41367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{BB18BFB1-C03A-41FE-BE1A-93D139757D6D}"/>
   </bookViews>
@@ -36,28 +36,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -267,6 +245,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -274,9 +255,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3526,33 +3504,33 @@
       <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="16" t="s">
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-      <c r="K3" s="16"/>
-      <c r="L3" s="16"/>
-      <c r="M3" s="16"/>
-      <c r="N3" s="16"/>
-      <c r="O3" s="16"/>
-      <c r="P3" s="16"/>
-      <c r="Q3" s="16"/>
-      <c r="R3" s="16"/>
-      <c r="S3" s="16"/>
-      <c r="U3" s="18" t="s">
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="17"/>
+      <c r="S3" s="17"/>
+      <c r="U3" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="V3" s="18"/>
-      <c r="W3" s="18"/>
+      <c r="V3" s="19"/>
+      <c r="W3" s="19"/>
     </row>
     <row r="4" spans="1:25" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="8"/>
@@ -3610,7 +3588,7 @@
       <c r="S4" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="U4" s="19" t="s">
+      <c r="U4" s="16" t="s">
         <v>20</v>
       </c>
       <c r="V4" s="8" t="s">
@@ -6133,35 +6111,35 @@
       </c>
       <c r="B40" s="12"/>
       <c r="C40" s="12"/>
-      <c r="D40" s="13" cm="1">
-        <f t="array" ref="D40">SUM(D5+D5:D19)</f>
+      <c r="D40" s="13">
+        <f>SUM(D5:D19)</f>
         <v>0</v>
       </c>
-      <c r="E40" s="13" cm="1">
-        <f t="array" ref="E40">SUM(E5+E5:E19)</f>
+      <c r="E40" s="13">
+        <f t="shared" ref="E40:G40" si="16">SUM(E5:E19)</f>
         <v>0</v>
       </c>
-      <c r="F40" s="13" cm="1">
-        <f t="array" ref="F40">SUM(F5+F5:F19)</f>
+      <c r="F40" s="13">
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="G40" s="13" cm="1">
-        <f t="array" ref="G40">SUM(G5+G5:G19)</f>
+      <c r="G40" s="13">
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="H40" s="12"/>
       <c r="I40" s="12"/>
-      <c r="J40" s="13" cm="1">
-        <f t="array" ref="J40">SUM(J5+J5:J19)</f>
-        <v>1510500</v>
-      </c>
-      <c r="K40" s="13" cm="1">
-        <f t="array" ref="K40">SUM(K5+K5:K19)</f>
-        <v>910500</v>
-      </c>
-      <c r="L40" s="13" cm="1">
-        <f t="array" ref="L40">SUM(L5+L5:L19)</f>
-        <v>2550</v>
+      <c r="J40" s="13">
+        <f t="shared" ref="J40:S40" si="17">SUM(J5:J19)</f>
+        <v>760500</v>
+      </c>
+      <c r="K40" s="13">
+        <f t="shared" si="17"/>
+        <v>460500</v>
+      </c>
+      <c r="L40" s="13">
+        <f t="shared" si="17"/>
+        <v>1800</v>
       </c>
       <c r="M40" s="11">
         <f>AVERAGE(M5:M19)</f>
@@ -6179,29 +6157,29 @@
         <f>AVERAGE(P5:P19)</f>
         <v>91.965609066958763</v>
       </c>
-      <c r="Q40" s="13" cm="1">
-        <f t="array" ref="Q40">SUM(Q5+Q5:Q19)</f>
+      <c r="Q40" s="13">
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="R40" s="13" cm="1">
-        <f t="array" ref="R40">SUM(R5+R5:R19)</f>
+      <c r="R40" s="13">
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="S40" s="13" cm="1">
-        <f t="array" ref="S40">SUM(S5+S5:S19)</f>
+      <c r="S40" s="13">
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="U40" s="13" cm="1">
-        <f t="array" ref="U40">SUM(U5+U5:U19)</f>
-        <v>602550</v>
-      </c>
-      <c r="V40" s="13" cm="1">
-        <f t="array" ref="V40">SUM(V5+V5:V19)</f>
-        <v>600000</v>
-      </c>
-      <c r="W40" s="13" cm="1">
-        <f t="array" ref="W40">SUM(W5+W5:W19)</f>
-        <v>602550</v>
+      <c r="U40" s="13">
+        <f t="shared" ref="U40:W40" si="18">SUM(U5:U19)</f>
+        <v>301800</v>
+      </c>
+      <c r="V40" s="13">
+        <f t="shared" si="18"/>
+        <v>300000</v>
+      </c>
+      <c r="W40" s="13">
+        <f t="shared" si="18"/>
+        <v>301800</v>
       </c>
     </row>
     <row r="41" spans="1:25" ht="15.6" x14ac:dyDescent="0.6">
@@ -6307,15 +6285,15 @@
       <c r="I42" s="12"/>
       <c r="J42" s="13">
         <f>J40+J41</f>
-        <v>2506100</v>
+        <v>1756100</v>
       </c>
       <c r="K42" s="13">
         <f>K40+K41</f>
-        <v>1526100</v>
+        <v>1076100</v>
       </c>
       <c r="L42" s="13">
         <f>L40+L41</f>
-        <v>8060</v>
+        <v>7310</v>
       </c>
       <c r="M42" s="11">
         <f>AVERAGE(M5:M38)</f>
@@ -6347,15 +6325,15 @@
       </c>
       <c r="U42" s="13">
         <f>U40+U41</f>
-        <v>988060</v>
+        <v>687310</v>
       </c>
       <c r="V42" s="13">
         <f>V40+V41</f>
-        <v>980000</v>
+        <v>680000</v>
       </c>
       <c r="W42" s="13">
         <f>W40+W41</f>
-        <v>988060</v>
+        <v>687310</v>
       </c>
     </row>
   </sheetData>
